--- a/Configs/skill_config.xlsx
+++ b/Configs/skill_config.xlsx
@@ -162,34 +162,34 @@
     <t>Self</t>
   </si>
   <si>
-    <t>60001|10001</t>
-  </si>
-  <si>
-    <t>60002|10002</t>
-  </si>
-  <si>
-    <t>60003|10003</t>
-  </si>
-  <si>
-    <t>60004|10004</t>
-  </si>
-  <si>
-    <t>60005|10005</t>
-  </si>
-  <si>
-    <t>60006|10006|70007</t>
-  </si>
-  <si>
-    <t>60007|10007|70007</t>
-  </si>
-  <si>
-    <t>60008|10008|70007</t>
-  </si>
-  <si>
-    <t>60009|10009|70007</t>
-  </si>
-  <si>
-    <t>60010|10010|70007|70008</t>
+    <t>60001|30001</t>
+  </si>
+  <si>
+    <t>60002|30002</t>
+  </si>
+  <si>
+    <t>60003|30003</t>
+  </si>
+  <si>
+    <t>60004|30004</t>
+  </si>
+  <si>
+    <t>60005|30005</t>
+  </si>
+  <si>
+    <t>60006|30006|70007</t>
+  </si>
+  <si>
+    <t>60007|30007|70007</t>
+  </si>
+  <si>
+    <t>60008|30008|70007</t>
+  </si>
+  <si>
+    <t>60009|30009|70007</t>
+  </si>
+  <si>
+    <t>60010|30010|70007|70008</t>
   </si>
   <si>
     <t>急冻冰锥</t>
@@ -204,34 +204,34 @@
     <t>Icon/solar-system-1-128</t>
   </si>
   <si>
-    <t>60011|10011|50001</t>
-  </si>
-  <si>
-    <t>60012|10011|50002</t>
-  </si>
-  <si>
-    <t>60013|10011|50003</t>
-  </si>
-  <si>
-    <t>60014|10011|50004</t>
-  </si>
-  <si>
-    <t>60015|10011|50005</t>
-  </si>
-  <si>
-    <t>60016|10011|50006</t>
-  </si>
-  <si>
-    <t>60017|10011|50007</t>
-  </si>
-  <si>
-    <t>60018|10011|50008</t>
-  </si>
-  <si>
-    <t>60019|10011|50009</t>
-  </si>
-  <si>
-    <t>60020|10011|50010</t>
+    <t>60011|30011|50001</t>
+  </si>
+  <si>
+    <t>60012|30011|50002</t>
+  </si>
+  <si>
+    <t>60013|30011|50003</t>
+  </si>
+  <si>
+    <t>60014|30011|50004</t>
+  </si>
+  <si>
+    <t>60015|30011|50005</t>
+  </si>
+  <si>
+    <t>60016|30011|50006</t>
+  </si>
+  <si>
+    <t>60017|30011|50007</t>
+  </si>
+  <si>
+    <t>60018|30011|50008</t>
+  </si>
+  <si>
+    <t>60019|30011|50009</t>
+  </si>
+  <si>
+    <t>60020|30011|50010</t>
   </si>
   <si>
     <t>闪电连锁</t>
@@ -1308,6 +1308,8 @@
   <dimension ref="A1:Q107"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
+    <col min="6" max="6" width="26" customWidth="1"/>
+    <col min="7" max="7" width="11.5" customWidth="1"/>
     <col min="10" max="10" width="12.625" customWidth="1"/>
     <col min="12" max="12" width="14.875" customWidth="1"/>
     <col min="13" max="13" width="13.75" customWidth="1"/>

--- a/Configs/skill_config.xlsx
+++ b/Configs/skill_config.xlsx
@@ -177,19 +177,19 @@
     <t>60005|30005</t>
   </si>
   <si>
-    <t>60006|30006|70007</t>
-  </si>
-  <si>
-    <t>60007|30007|70007</t>
-  </si>
-  <si>
-    <t>60008|30008|70007</t>
-  </si>
-  <si>
-    <t>60009|30009|70007</t>
-  </si>
-  <si>
-    <t>60010|30010|70007|70008</t>
+    <t>60006|30006|70400</t>
+  </si>
+  <si>
+    <t>60007|30007|70400</t>
+  </si>
+  <si>
+    <t>60008|30008|70400</t>
+  </si>
+  <si>
+    <t>60009|30009|70400</t>
+  </si>
+  <si>
+    <t>60010|30010|70400|70500</t>
   </si>
   <si>
     <t>急冻冰锥</t>
@@ -2363,7 +2363,7 @@
         <v>12</v>
       </c>
       <c r="K21">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="L21">
         <v>101</v>
@@ -2415,7 +2415,7 @@
         <v>12</v>
       </c>
       <c r="K22">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="L22">
         <v>101</v>
@@ -2467,7 +2467,7 @@
         <v>12</v>
       </c>
       <c r="K23">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="L23">
         <v>101</v>
@@ -2519,7 +2519,7 @@
         <v>12</v>
       </c>
       <c r="K24">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="L24">
         <v>101</v>
@@ -2571,7 +2571,7 @@
         <v>12</v>
       </c>
       <c r="K25">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="L25">
         <v>101</v>
@@ -2623,7 +2623,7 @@
         <v>12</v>
       </c>
       <c r="K26">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="L26">
         <v>101</v>
@@ -2635,7 +2635,7 @@
         <v>60006</v>
       </c>
       <c r="O26" s="1">
-        <v>70100</v>
+        <v>70010</v>
       </c>
       <c r="P26">
         <v>201006</v>
@@ -2675,7 +2675,7 @@
         <v>12</v>
       </c>
       <c r="K27">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="L27">
         <v>101</v>
@@ -2687,7 +2687,7 @@
         <v>60007</v>
       </c>
       <c r="O27" s="1">
-        <v>70100</v>
+        <v>70010</v>
       </c>
       <c r="P27">
         <v>201007</v>
@@ -2727,7 +2727,7 @@
         <v>12</v>
       </c>
       <c r="K28">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="L28">
         <v>101</v>
@@ -2739,7 +2739,7 @@
         <v>60008</v>
       </c>
       <c r="O28" s="1">
-        <v>70100</v>
+        <v>70010</v>
       </c>
       <c r="P28">
         <v>201008</v>
@@ -2779,7 +2779,7 @@
         <v>12</v>
       </c>
       <c r="K29">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="L29">
         <v>101</v>
@@ -2791,7 +2791,7 @@
         <v>60009</v>
       </c>
       <c r="O29" s="1">
-        <v>70100</v>
+        <v>70010</v>
       </c>
       <c r="P29">
         <v>201009</v>
@@ -2831,7 +2831,7 @@
         <v>12</v>
       </c>
       <c r="K30">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="L30">
         <v>101</v>
@@ -2843,7 +2843,7 @@
         <v>60010</v>
       </c>
       <c r="O30" s="1">
-        <v>70100</v>
+        <v>70010</v>
       </c>
       <c r="P30" t="s">
         <v>40</v>
@@ -2883,7 +2883,7 @@
         <v>0</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -2935,7 +2935,7 @@
         <v>0</v>
       </c>
       <c r="K32">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -2981,7 +2981,7 @@
         <v>0</v>
       </c>
       <c r="K33">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -3027,7 +3027,7 @@
         <v>0</v>
       </c>
       <c r="K34">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -3073,7 +3073,7 @@
         <v>0</v>
       </c>
       <c r="K35">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -3119,7 +3119,7 @@
         <v>0</v>
       </c>
       <c r="K36">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -3165,7 +3165,7 @@
         <v>0</v>
       </c>
       <c r="K37">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -3212,7 +3212,7 @@
         <v>0</v>
       </c>
       <c r="K38">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -3259,7 +3259,7 @@
         <v>0</v>
       </c>
       <c r="K39">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -3306,7 +3306,7 @@
         <v>0</v>
       </c>
       <c r="K40">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -3353,7 +3353,7 @@
         <v>0</v>
       </c>
       <c r="K41">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -3400,7 +3400,7 @@
         <v>0</v>
       </c>
       <c r="K42">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L42">
         <v>102</v>
@@ -3452,7 +3452,7 @@
         <v>15</v>
       </c>
       <c r="K43">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="L43">
         <v>102</v>
@@ -3504,7 +3504,7 @@
         <v>15</v>
       </c>
       <c r="K44">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="L44">
         <v>102</v>
@@ -3556,7 +3556,7 @@
         <v>15</v>
       </c>
       <c r="K45">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="L45">
         <v>102</v>
@@ -3608,7 +3608,7 @@
         <v>15</v>
       </c>
       <c r="K46">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="L46">
         <v>102</v>
@@ -3660,7 +3660,7 @@
         <v>15</v>
       </c>
       <c r="K47">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="L47">
         <v>102</v>
@@ -3712,7 +3712,7 @@
         <v>15</v>
       </c>
       <c r="K48">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="L48">
         <v>102</v>
@@ -3764,7 +3764,7 @@
         <v>15</v>
       </c>
       <c r="K49">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="L49">
         <v>102</v>
@@ -3816,7 +3816,7 @@
         <v>15</v>
       </c>
       <c r="K50">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="L50">
         <v>102</v>
@@ -3868,7 +3868,7 @@
         <v>15</v>
       </c>
       <c r="K51">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="L51">
         <v>102</v>
@@ -3920,7 +3920,7 @@
         <v>15</v>
       </c>
       <c r="K52">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="L52">
         <v>102</v>
@@ -3972,7 +3972,7 @@
         <v>0</v>
       </c>
       <c r="K53">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L53">
         <v>0</v>
@@ -4024,7 +4024,7 @@
         <v>0</v>
       </c>
       <c r="K54">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="L54">
         <v>0</v>
@@ -4073,7 +4073,7 @@
         <v>0</v>
       </c>
       <c r="K55">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -4122,7 +4122,7 @@
         <v>0</v>
       </c>
       <c r="K56">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="L56">
         <v>0</v>
@@ -4171,7 +4171,7 @@
         <v>0</v>
       </c>
       <c r="K57">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="L57">
         <v>0</v>
@@ -4220,7 +4220,7 @@
         <v>0</v>
       </c>
       <c r="K58">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="L58">
         <v>0</v>
@@ -4269,7 +4269,7 @@
         <v>0</v>
       </c>
       <c r="K59">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="L59">
         <v>0</v>
@@ -4318,7 +4318,7 @@
         <v>0</v>
       </c>
       <c r="K60">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="L60">
         <v>0</v>
@@ -4367,7 +4367,7 @@
         <v>0</v>
       </c>
       <c r="K61">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="L61">
         <v>0</v>
@@ -4416,7 +4416,7 @@
         <v>0</v>
       </c>
       <c r="K62">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="L62">
         <v>0</v>
@@ -4465,7 +4465,7 @@
         <v>0</v>
       </c>
       <c r="K63">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="L63">
         <v>0</v>
@@ -4514,7 +4514,7 @@
         <v>0</v>
       </c>
       <c r="K64">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L64">
         <v>103</v>
@@ -4566,7 +4566,7 @@
         <v>20</v>
       </c>
       <c r="K65">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="L65">
         <v>103</v>
@@ -4618,7 +4618,7 @@
         <v>20</v>
       </c>
       <c r="K66">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="L66">
         <v>103</v>
@@ -4670,7 +4670,7 @@
         <v>20</v>
       </c>
       <c r="K67">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="L67">
         <v>103</v>
@@ -4722,7 +4722,7 @@
         <v>20</v>
       </c>
       <c r="K68">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="L68">
         <v>103</v>
@@ -4774,7 +4774,7 @@
         <v>20</v>
       </c>
       <c r="K69">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="L69">
         <v>103</v>
@@ -4826,7 +4826,7 @@
         <v>20</v>
       </c>
       <c r="K70">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="L70">
         <v>103</v>
@@ -4878,7 +4878,7 @@
         <v>20</v>
       </c>
       <c r="K71">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="L71">
         <v>103</v>
@@ -4930,7 +4930,7 @@
         <v>20</v>
       </c>
       <c r="K72">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="L72">
         <v>103</v>
@@ -4982,7 +4982,7 @@
         <v>20</v>
       </c>
       <c r="K73">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="L73">
         <v>103</v>
@@ -5034,7 +5034,7 @@
         <v>20</v>
       </c>
       <c r="K74">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="L74">
         <v>103</v>
@@ -5086,7 +5086,7 @@
         <v>0</v>
       </c>
       <c r="K75">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L75">
         <v>104</v>
@@ -5138,7 +5138,7 @@
         <v>0</v>
       </c>
       <c r="K76">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="L76">
         <v>104</v>
@@ -5190,7 +5190,7 @@
         <v>0</v>
       </c>
       <c r="K77">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="L77">
         <v>104</v>
@@ -5242,7 +5242,7 @@
         <v>0</v>
       </c>
       <c r="K78">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="L78">
         <v>104</v>
@@ -5294,7 +5294,7 @@
         <v>0</v>
       </c>
       <c r="K79">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="L79">
         <v>104</v>
@@ -5346,7 +5346,7 @@
         <v>0</v>
       </c>
       <c r="K80">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="L80">
         <v>104</v>
@@ -5398,7 +5398,7 @@
         <v>0</v>
       </c>
       <c r="K81">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="L81">
         <v>104</v>
@@ -5447,7 +5447,7 @@
         <v>0</v>
       </c>
       <c r="K82">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="L82">
         <v>104</v>
@@ -5496,7 +5496,7 @@
         <v>0</v>
       </c>
       <c r="K83">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="L83">
         <v>104</v>
@@ -5545,7 +5545,7 @@
         <v>0</v>
       </c>
       <c r="K84">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="L84">
         <v>104</v>
@@ -5594,7 +5594,7 @@
         <v>0</v>
       </c>
       <c r="K85">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="L85">
         <v>104</v>
@@ -5640,7 +5640,7 @@
         <v>0</v>
       </c>
       <c r="K86">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L86">
         <v>0</v>
@@ -5692,7 +5692,7 @@
         <v>0</v>
       </c>
       <c r="K87">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="L87">
         <v>0</v>
@@ -5744,7 +5744,7 @@
         <v>0</v>
       </c>
       <c r="K88">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="L88">
         <v>0</v>
@@ -5796,7 +5796,7 @@
         <v>0</v>
       </c>
       <c r="K89">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="L89">
         <v>0</v>
@@ -5848,7 +5848,7 @@
         <v>0</v>
       </c>
       <c r="K90">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="L90">
         <v>0</v>
@@ -5900,7 +5900,7 @@
         <v>0</v>
       </c>
       <c r="K91">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="L91">
         <v>0</v>
@@ -5952,7 +5952,7 @@
         <v>0</v>
       </c>
       <c r="K92">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="L92">
         <v>0</v>
@@ -6004,7 +6004,7 @@
         <v>0</v>
       </c>
       <c r="K93">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="L93">
         <v>0</v>
@@ -6056,7 +6056,7 @@
         <v>0</v>
       </c>
       <c r="K94">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="L94">
         <v>0</v>
@@ -6108,7 +6108,7 @@
         <v>0</v>
       </c>
       <c r="K95">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="L95">
         <v>0</v>
@@ -6160,7 +6160,7 @@
         <v>0</v>
       </c>
       <c r="K96">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="L96">
         <v>0</v>
@@ -6212,7 +6212,7 @@
         <v>0</v>
       </c>
       <c r="K97">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L97">
         <v>0</v>
@@ -6264,7 +6264,7 @@
         <v>0</v>
       </c>
       <c r="K98">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="L98">
         <v>0</v>
@@ -6313,7 +6313,7 @@
         <v>0</v>
       </c>
       <c r="K99">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="L99">
         <v>0</v>
@@ -6362,7 +6362,7 @@
         <v>0</v>
       </c>
       <c r="K100">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="L100">
         <v>0</v>
@@ -6411,7 +6411,7 @@
         <v>0</v>
       </c>
       <c r="K101">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="L101">
         <v>0</v>
@@ -6460,7 +6460,7 @@
         <v>0</v>
       </c>
       <c r="K102">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="L102">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="K103">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="L103">
         <v>0</v>
@@ -6558,7 +6558,7 @@
         <v>0</v>
       </c>
       <c r="K104">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="L104">
         <v>0</v>
@@ -6607,7 +6607,7 @@
         <v>0</v>
       </c>
       <c r="K105">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="L105">
         <v>0</v>
@@ -6656,7 +6656,7 @@
         <v>0</v>
       </c>
       <c r="K106">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="L106">
         <v>0</v>
@@ -6705,7 +6705,7 @@
         <v>0</v>
       </c>
       <c r="K107">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="L107">
         <v>0</v>

--- a/Configs/skill_config.xlsx
+++ b/Configs/skill_config.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="103">
   <si>
     <t>id</t>
   </si>
@@ -108,15 +108,18 @@
     <t>追踪风弹</t>
   </si>
   <si>
+    <t>追踪穿刺风弹</t>
+  </si>
+  <si>
+    <t>103000|101002</t>
+  </si>
+  <si>
     <t>岩弹</t>
   </si>
   <si>
     <t>全屏反击</t>
   </si>
   <si>
-    <t>TODO 附加减速和击退</t>
-  </si>
-  <si>
     <t>Aoe</t>
   </si>
   <si>
@@ -129,18 +132,6 @@
     <t>反击穿刺盾弹</t>
   </si>
   <si>
-    <t>201006|101000</t>
-  </si>
-  <si>
-    <t>201007|101000</t>
-  </si>
-  <si>
-    <t>201008|101000</t>
-  </si>
-  <si>
-    <t>201009|101000</t>
-  </si>
-  <si>
     <t>201010|101000</t>
   </si>
   <si>
@@ -150,7 +141,7 @@
     <t>Icon/commet-128</t>
   </si>
   <si>
-    <t>201010|102001</t>
+    <t>201008|102001</t>
   </si>
   <si>
     <t>治愈圣火</t>
@@ -162,34 +153,34 @@
     <t>Self</t>
   </si>
   <si>
-    <t>60001|30001</t>
-  </si>
-  <si>
-    <t>60002|30002</t>
-  </si>
-  <si>
-    <t>60003|30003</t>
-  </si>
-  <si>
-    <t>60004|30004</t>
-  </si>
-  <si>
-    <t>60005|30005</t>
-  </si>
-  <si>
-    <t>60006|30006|70400</t>
-  </si>
-  <si>
-    <t>60007|30007|70400</t>
-  </si>
-  <si>
-    <t>60008|30008|70400</t>
-  </si>
-  <si>
-    <t>60009|30009|70400</t>
-  </si>
-  <si>
-    <t>60010|30010|70400|70500</t>
+    <t>60001|10001</t>
+  </si>
+  <si>
+    <t>60002|10002</t>
+  </si>
+  <si>
+    <t>60003|10003|30001</t>
+  </si>
+  <si>
+    <t>60004|10004|30001</t>
+  </si>
+  <si>
+    <t>60005|10005|30003</t>
+  </si>
+  <si>
+    <t>60006|10006|30003</t>
+  </si>
+  <si>
+    <t>60007|10007|30003</t>
+  </si>
+  <si>
+    <t>60008|10008|30003|70400</t>
+  </si>
+  <si>
+    <t>60009|10009|30003|70400</t>
+  </si>
+  <si>
+    <t>60010|10010|30003|70400|80001</t>
   </si>
   <si>
     <t>急冻冰锥</t>
@@ -198,7 +189,13 @@
     <t>Icon/skull-128</t>
   </si>
   <si>
-    <t>血能交换</t>
+    <t>201005|101000</t>
+  </si>
+  <si>
+    <t>201005|101000|70601</t>
+  </si>
+  <si>
+    <t>能量泉源</t>
   </si>
   <si>
     <t>Icon/solar-system-1-128</t>
@@ -210,28 +207,28 @@
     <t>60012|30011|50002</t>
   </si>
   <si>
-    <t>60013|30011|50003</t>
-  </si>
-  <si>
-    <t>60014|30011|50004</t>
-  </si>
-  <si>
-    <t>60015|30011|50005</t>
-  </si>
-  <si>
-    <t>60016|30011|50006</t>
-  </si>
-  <si>
-    <t>60017|30011|50007</t>
-  </si>
-  <si>
-    <t>60018|30011|50008</t>
-  </si>
-  <si>
-    <t>60019|30011|50009</t>
-  </si>
-  <si>
-    <t>60020|30011|50010</t>
+    <t>60013|30012|50003</t>
+  </si>
+  <si>
+    <t>60014|30012|50004</t>
+  </si>
+  <si>
+    <t>60015|30012|50005</t>
+  </si>
+  <si>
+    <t>60016|30012|50006</t>
+  </si>
+  <si>
+    <t>60017|30012|50007</t>
+  </si>
+  <si>
+    <t>60018|50008</t>
+  </si>
+  <si>
+    <t>60019|50009</t>
+  </si>
+  <si>
+    <t>60020|50010</t>
   </si>
   <si>
     <t>闪电连锁</t>
@@ -240,6 +237,9 @@
     <t>Icon/satellite-128</t>
   </si>
   <si>
+    <t>202003|102002</t>
+  </si>
+  <si>
     <t>电磁盾牌</t>
   </si>
   <si>
@@ -249,31 +249,31 @@
     <t>Shield</t>
   </si>
   <si>
-    <t>60021|20001|70700</t>
-  </si>
-  <si>
-    <t>60022|20002|70701</t>
+    <t>60021|20001</t>
+  </si>
+  <si>
+    <t>60022|20002</t>
   </si>
   <si>
     <t>60023|20003|70702</t>
   </si>
   <si>
-    <t>60024|20004|70703</t>
-  </si>
-  <si>
-    <t>60025|20005|70704</t>
-  </si>
-  <si>
-    <t>60026|20006|70705</t>
-  </si>
-  <si>
-    <t>60027|20007|70706</t>
-  </si>
-  <si>
-    <t>60028|20008|70707</t>
-  </si>
-  <si>
-    <t>60029|20009|70708</t>
+    <t>60024|20004|70702</t>
+  </si>
+  <si>
+    <t>60025|20005|70709</t>
+  </si>
+  <si>
+    <t>60026|20006|70709</t>
+  </si>
+  <si>
+    <t>60027|20007|70709</t>
+  </si>
+  <si>
+    <t>60028|20008|70709</t>
+  </si>
+  <si>
+    <t>60029|20009|70709</t>
   </si>
   <si>
     <t>60030|20010|70709|80001</t>
@@ -285,19 +285,13 @@
     <t>Icon/black-hole-128</t>
   </si>
   <si>
-    <t>40006|70301</t>
-  </si>
-  <si>
-    <t>40007|70301</t>
-  </si>
-  <si>
-    <t>40008|70301</t>
-  </si>
-  <si>
-    <t>40009|70301</t>
+    <t>40003|70301</t>
   </si>
   <si>
     <t>40010|70301</t>
+  </si>
+  <si>
+    <t>60040|70600</t>
   </si>
   <si>
     <t>风影守卫</t>
@@ -1305,7 +1299,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q107"/>
+  <dimension ref="A1:Q101"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="6" max="6" width="26" customWidth="1"/>
@@ -1419,7 +1413,7 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="1">
-        <f t="shared" ref="A3:A10" si="0">B3*100+C3</f>
+        <f t="shared" ref="A3:A7" si="0">B3*100+C3</f>
         <v>1000001</v>
       </c>
       <c r="B3" s="1">
@@ -1618,23 +1612,20 @@
         <v>103000</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" customFormat="1" spans="1:16">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
-        <v>1000301</v>
+        <v>1000203</v>
       </c>
       <c r="B7" s="1">
-        <v>10003</v>
+        <v>10002</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D7" t="s">
         <v>26</v>
       </c>
-      <c r="E7" t="s">
-        <v>21</v>
-      </c>
       <c r="F7" t="s">
         <v>21</v>
       </c>
@@ -1666,46 +1657,49 @@
         <v>21</v>
       </c>
       <c r="P7" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="1">
-        <f t="shared" si="0"/>
-        <v>1000401</v>
+        <f>B8*100+C8</f>
+        <v>1000301</v>
       </c>
       <c r="B8" s="1">
-        <v>10004</v>
+        <v>10003</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E8" t="s">
-        <v>28</v>
+        <v>21</v>
+      </c>
+      <c r="F8" t="s">
+        <v>21</v>
       </c>
       <c r="G8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="H8">
-        <v>3000</v>
+        <v>10000</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N8" t="s">
         <v>21</v>
@@ -1719,50 +1713,45 @@
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="1">
-        <f t="shared" si="0"/>
-        <v>2000001</v>
-      </c>
-      <c r="B9">
-        <v>20000</v>
+        <f>B9*100+C9</f>
+        <v>1000401</v>
+      </c>
+      <c r="B9" s="1">
+        <v>10004</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9"/>
+      <c r="G9" t="s">
         <v>30</v>
       </c>
-      <c r="E9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9" t="s">
-        <v>21</v>
-      </c>
-      <c r="G9" t="s">
-        <v>22</v>
-      </c>
       <c r="H9">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K9">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="L9">
-        <v>201</v>
+        <v>0</v>
       </c>
       <c r="M9">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N9" t="s">
         <v>21</v>
       </c>
-      <c r="O9" t="s">
-        <v>21</v>
+      <c r="O9">
+        <v>40003</v>
       </c>
       <c r="P9" t="s">
         <v>21</v>
@@ -1770,11 +1759,11 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="1">
-        <f t="shared" si="0"/>
-        <v>1006101</v>
-      </c>
-      <c r="B10" s="1">
-        <v>10061</v>
+        <f>B10*100+C10</f>
+        <v>2000001</v>
+      </c>
+      <c r="B10">
+        <v>20000</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -1798,16 +1787,16 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L10">
-        <v>1</v>
+        <v>201</v>
       </c>
       <c r="M10">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="N10" t="s">
         <v>21</v>
@@ -1821,17 +1810,17 @@
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="1">
-        <f t="shared" ref="A10:A20" si="1">B11*100+C11</f>
-        <v>1006102</v>
+        <f>B11*100+C11</f>
+        <v>1006101</v>
       </c>
       <c r="B11" s="1">
         <v>10061</v>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
         <v>21</v>
@@ -1843,7 +1832,7 @@
         <v>22</v>
       </c>
       <c r="H11">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -1867,22 +1856,22 @@
         <v>21</v>
       </c>
       <c r="P11">
-        <v>201002</v>
+        <v>201003</v>
       </c>
     </row>
     <row r="12" spans="1:16">
       <c r="A12" s="1">
-        <f t="shared" si="1"/>
-        <v>1006103</v>
+        <f>B12*100+C12</f>
+        <v>1006102</v>
       </c>
       <c r="B12" s="1">
         <v>10061</v>
       </c>
       <c r="C12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E12" t="s">
         <v>21</v>
@@ -1894,7 +1883,7 @@
         <v>22</v>
       </c>
       <c r="H12">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -1918,22 +1907,22 @@
         <v>21</v>
       </c>
       <c r="P12">
-        <v>201003</v>
+        <v>201010</v>
       </c>
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="1">
-        <f t="shared" si="1"/>
-        <v>1006104</v>
+        <f>B13*100+C13</f>
+        <v>1006103</v>
       </c>
       <c r="B13" s="1">
         <v>10061</v>
       </c>
       <c r="C13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E13" t="s">
         <v>21</v>
@@ -1945,7 +1934,7 @@
         <v>22</v>
       </c>
       <c r="H13">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -1968,50 +1957,50 @@
       <c r="O13" t="s">
         <v>21</v>
       </c>
-      <c r="P13">
-        <v>201004</v>
+      <c r="P13" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="1">
-        <f t="shared" si="1"/>
-        <v>1006105</v>
+        <f t="shared" ref="A14:A77" si="1">B14*100+C14</f>
+        <v>100100</v>
       </c>
       <c r="B14" s="1">
-        <v>10061</v>
+        <v>1001</v>
       </c>
       <c r="C14">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D14" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E14" t="s">
         <v>21</v>
       </c>
       <c r="F14" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="G14" t="s">
         <v>22</v>
       </c>
       <c r="H14">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K14">
         <v>0</v>
       </c>
       <c r="L14">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="M14">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="N14" t="s">
         <v>21</v>
@@ -2019,29 +2008,30 @@
       <c r="O14" t="s">
         <v>21</v>
       </c>
-      <c r="P14">
-        <v>201005</v>
+      <c r="P14" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="1">
         <f t="shared" si="1"/>
-        <v>1006106</v>
+        <v>100101</v>
       </c>
       <c r="B15" s="1">
-        <v>10061</v>
+        <f t="shared" ref="B15:B24" si="2">B14</f>
+        <v>1001</v>
       </c>
       <c r="C15">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D15" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E15" t="s">
         <v>21</v>
       </c>
       <c r="F15" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="G15" t="s">
         <v>22</v>
@@ -2050,268 +2040,270 @@
         <v>10000</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L15">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="M15">
-        <v>50</v>
-      </c>
-      <c r="N15" t="s">
-        <v>21</v>
+        <v>30</v>
+      </c>
+      <c r="N15">
+        <v>60001</v>
       </c>
       <c r="O15" t="s">
         <v>21</v>
       </c>
       <c r="P15" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="1">
         <f t="shared" si="1"/>
-        <v>1006107</v>
+        <v>100102</v>
       </c>
       <c r="B16" s="1">
-        <v>10061</v>
+        <f t="shared" si="2"/>
+        <v>1001</v>
       </c>
       <c r="C16">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D16" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E16" t="s">
         <v>21</v>
       </c>
       <c r="F16" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="G16" t="s">
         <v>22</v>
       </c>
       <c r="H16">
-        <v>10000</v>
+        <v>11000</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L16">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="M16">
-        <v>50</v>
-      </c>
-      <c r="N16" t="s">
-        <v>21</v>
+        <v>30</v>
+      </c>
+      <c r="N16">
+        <v>60002</v>
       </c>
       <c r="O16" t="s">
         <v>21</v>
       </c>
-      <c r="P16" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16">
+    </row>
+    <row r="17" spans="1:17">
       <c r="A17" s="1">
         <f t="shared" si="1"/>
-        <v>1006108</v>
+        <v>100103</v>
       </c>
       <c r="B17" s="1">
-        <v>10061</v>
+        <f t="shared" si="2"/>
+        <v>1001</v>
       </c>
       <c r="C17">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D17" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E17" t="s">
         <v>21</v>
       </c>
       <c r="F17" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="G17" t="s">
         <v>22</v>
       </c>
       <c r="H17">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L17">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="M17">
-        <v>50</v>
-      </c>
-      <c r="N17" t="s">
-        <v>21</v>
+        <v>30</v>
+      </c>
+      <c r="N17">
+        <v>60003</v>
       </c>
       <c r="O17" t="s">
         <v>21</v>
       </c>
-      <c r="P17" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16">
+      <c r="P17">
+        <v>201004</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17">
       <c r="A18" s="1">
         <f t="shared" si="1"/>
-        <v>1006109</v>
+        <v>100104</v>
       </c>
       <c r="B18" s="1">
-        <v>10061</v>
+        <f t="shared" si="2"/>
+        <v>1001</v>
       </c>
       <c r="C18">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D18" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E18" t="s">
         <v>21</v>
       </c>
       <c r="F18" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="G18" t="s">
         <v>22</v>
       </c>
       <c r="H18">
-        <v>10000</v>
+        <v>13000</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L18">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="M18">
-        <v>50</v>
-      </c>
-      <c r="N18" t="s">
-        <v>21</v>
+        <v>30</v>
+      </c>
+      <c r="N18">
+        <v>60004</v>
       </c>
       <c r="O18" t="s">
         <v>21</v>
       </c>
-      <c r="P18" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16">
+      <c r="P18">
+        <v>201004</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17">
       <c r="A19" s="1">
         <f t="shared" si="1"/>
-        <v>1006110</v>
+        <v>100105</v>
       </c>
       <c r="B19" s="1">
-        <v>10061</v>
+        <f t="shared" si="2"/>
+        <v>1001</v>
       </c>
       <c r="C19">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D19" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E19" t="s">
         <v>21</v>
       </c>
       <c r="F19" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="G19" t="s">
         <v>22</v>
       </c>
       <c r="H19">
-        <v>10000</v>
+        <v>14000</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L19">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="M19">
-        <v>50</v>
-      </c>
-      <c r="N19" t="s">
-        <v>21</v>
+        <v>30</v>
+      </c>
+      <c r="N19">
+        <v>60005</v>
       </c>
       <c r="O19" t="s">
         <v>21</v>
       </c>
-      <c r="P19" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16">
+      <c r="P19">
+        <v>201008</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17">
       <c r="A20" s="1">
-        <f t="shared" ref="A20:A83" si="2">B20*100+C20</f>
-        <v>100100</v>
+        <f t="shared" si="1"/>
+        <v>100106</v>
       </c>
       <c r="B20" s="1">
+        <f t="shared" si="2"/>
         <v>1001</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D20" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E20" t="s">
         <v>21</v>
       </c>
       <c r="F20" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G20" t="s">
         <v>22</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I20">
         <v>1</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L20">
         <v>101</v>
@@ -2319,42 +2311,40 @@
       <c r="M20">
         <v>30</v>
       </c>
-      <c r="N20" t="s">
-        <v>21</v>
-      </c>
-      <c r="O20" t="s">
-        <v>21</v>
-      </c>
-      <c r="P20" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16">
+      <c r="N20">
+        <v>60006</v>
+      </c>
+      <c r="O20" s="1"/>
+      <c r="P20">
+        <v>201008</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17">
       <c r="A21" s="1">
+        <f t="shared" si="1"/>
+        <v>100107</v>
+      </c>
+      <c r="B21" s="1">
         <f t="shared" si="2"/>
-        <v>100101</v>
-      </c>
-      <c r="B21" s="1">
-        <f t="shared" ref="B21:B30" si="3">B20</f>
         <v>1001</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D21" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E21" t="s">
         <v>21</v>
       </c>
       <c r="F21" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G21" t="s">
         <v>22</v>
       </c>
       <c r="H21">
-        <v>10000</v>
+        <v>16000</v>
       </c>
       <c r="I21">
         <v>1</v>
@@ -2372,41 +2362,39 @@
         <v>30</v>
       </c>
       <c r="N21">
-        <v>60001</v>
-      </c>
-      <c r="O21" t="s">
-        <v>21</v>
-      </c>
-      <c r="P21" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16">
+        <v>60007</v>
+      </c>
+      <c r="O21" s="1"/>
+      <c r="P21">
+        <v>201008</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17">
       <c r="A22" s="1">
+        <f t="shared" si="1"/>
+        <v>100108</v>
+      </c>
+      <c r="B22" s="1">
         <f t="shared" si="2"/>
-        <v>100102</v>
-      </c>
-      <c r="B22" s="1">
-        <f t="shared" si="3"/>
         <v>1001</v>
       </c>
       <c r="C22">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E22" t="s">
         <v>21</v>
       </c>
       <c r="F22" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G22" t="s">
         <v>22</v>
       </c>
       <c r="H22">
-        <v>10000</v>
+        <v>17000</v>
       </c>
       <c r="I22">
         <v>1</v>
@@ -2424,41 +2412,41 @@
         <v>30</v>
       </c>
       <c r="N22">
-        <v>60002</v>
-      </c>
-      <c r="O22" t="s">
-        <v>21</v>
+        <v>60008</v>
+      </c>
+      <c r="O22" s="1">
+        <v>70010</v>
       </c>
       <c r="P22">
-        <v>201002</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16">
+        <v>201008</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17">
       <c r="A23" s="1">
+        <f t="shared" si="1"/>
+        <v>100109</v>
+      </c>
+      <c r="B23" s="1">
         <f t="shared" si="2"/>
-        <v>100103</v>
-      </c>
-      <c r="B23" s="1">
-        <f t="shared" si="3"/>
         <v>1001</v>
       </c>
       <c r="C23">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D23" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E23" t="s">
         <v>21</v>
       </c>
       <c r="F23" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G23" t="s">
         <v>22</v>
       </c>
       <c r="H23">
-        <v>10000</v>
+        <v>18000</v>
       </c>
       <c r="I23">
         <v>1</v>
@@ -2476,41 +2464,41 @@
         <v>30</v>
       </c>
       <c r="N23">
-        <v>60003</v>
-      </c>
-      <c r="O23" t="s">
-        <v>21</v>
+        <v>60009</v>
+      </c>
+      <c r="O23" s="1">
+        <v>70010</v>
       </c>
       <c r="P23">
-        <v>201003</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16">
+        <v>201008</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17">
       <c r="A24" s="1">
+        <f t="shared" si="1"/>
+        <v>100110</v>
+      </c>
+      <c r="B24" s="1">
         <f t="shared" si="2"/>
-        <v>100104</v>
-      </c>
-      <c r="B24" s="1">
-        <f t="shared" si="3"/>
         <v>1001</v>
       </c>
       <c r="C24">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D24" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E24" t="s">
         <v>21</v>
       </c>
       <c r="F24" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G24" t="s">
         <v>22</v>
       </c>
       <c r="H24">
-        <v>10000</v>
+        <v>19000</v>
       </c>
       <c r="I24">
         <v>1</v>
@@ -2528,26 +2516,26 @@
         <v>30</v>
       </c>
       <c r="N24">
-        <v>60004</v>
-      </c>
-      <c r="O24" t="s">
-        <v>21</v>
-      </c>
-      <c r="P24">
-        <v>201004</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16">
+        <v>60010</v>
+      </c>
+      <c r="O24" s="1">
+        <v>70010</v>
+      </c>
+      <c r="P24" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17">
       <c r="A25" s="1">
-        <f t="shared" si="2"/>
-        <v>100105</v>
+        <f t="shared" si="1"/>
+        <v>100200</v>
       </c>
       <c r="B25" s="1">
-        <f t="shared" si="3"/>
-        <v>1001</v>
+        <f>B14+1</f>
+        <v>1002</v>
       </c>
       <c r="C25">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D25" t="s">
         <v>38</v>
@@ -2559,47 +2547,47 @@
         <v>39</v>
       </c>
       <c r="G25" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="H25">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="I25">
         <v>1</v>
       </c>
       <c r="J25">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K25">
         <v>3</v>
       </c>
       <c r="L25">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="M25">
-        <v>30</v>
-      </c>
-      <c r="N25">
-        <v>60005</v>
+        <v>0</v>
+      </c>
+      <c r="N25" t="s">
+        <v>21</v>
       </c>
       <c r="O25" t="s">
         <v>21</v>
       </c>
-      <c r="P25">
-        <v>201005</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16">
+      <c r="P25" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17">
       <c r="A26" s="1">
-        <f t="shared" si="2"/>
-        <v>100106</v>
+        <f t="shared" si="1"/>
+        <v>100201</v>
       </c>
       <c r="B26" s="1">
-        <f t="shared" si="3"/>
-        <v>1001</v>
+        <f t="shared" ref="B26:B35" si="3">B25</f>
+        <v>1002</v>
       </c>
       <c r="C26">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D26" t="s">
         <v>38</v>
@@ -2611,47 +2599,41 @@
         <v>39</v>
       </c>
       <c r="G26" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="H26">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="I26">
         <v>1</v>
       </c>
       <c r="J26">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K26">
         <v>3</v>
       </c>
       <c r="L26">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="M26">
-        <v>30</v>
-      </c>
-      <c r="N26">
-        <v>60006</v>
-      </c>
-      <c r="O26" s="1">
-        <v>70010</v>
-      </c>
-      <c r="P26">
-        <v>201006</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="N26" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17">
       <c r="A27" s="1">
-        <f t="shared" si="2"/>
-        <v>100107</v>
+        <f t="shared" si="1"/>
+        <v>100202</v>
       </c>
       <c r="B27" s="1">
         <f t="shared" si="3"/>
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="C27">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D27" t="s">
         <v>38</v>
@@ -2663,47 +2645,41 @@
         <v>39</v>
       </c>
       <c r="G27" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="H27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="I27">
         <v>1</v>
       </c>
       <c r="J27">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K27">
         <v>3</v>
       </c>
       <c r="L27">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="M27">
-        <v>30</v>
-      </c>
-      <c r="N27">
-        <v>60007</v>
-      </c>
-      <c r="O27" s="1">
-        <v>70010</v>
-      </c>
-      <c r="P27">
-        <v>201007</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="N27" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17">
       <c r="A28" s="1">
-        <f t="shared" si="2"/>
-        <v>100108</v>
+        <f t="shared" si="1"/>
+        <v>100203</v>
       </c>
       <c r="B28" s="1">
         <f t="shared" si="3"/>
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="C28">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D28" t="s">
         <v>38</v>
@@ -2715,47 +2691,41 @@
         <v>39</v>
       </c>
       <c r="G28" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="H28">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="I28">
         <v>1</v>
       </c>
       <c r="J28">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K28">
         <v>3</v>
       </c>
       <c r="L28">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="M28">
-        <v>30</v>
-      </c>
-      <c r="N28">
-        <v>60008</v>
-      </c>
-      <c r="O28" s="1">
-        <v>70010</v>
-      </c>
-      <c r="P28">
-        <v>201008</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="N28" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17">
       <c r="A29" s="1">
-        <f t="shared" si="2"/>
-        <v>100109</v>
+        <f t="shared" si="1"/>
+        <v>100204</v>
       </c>
       <c r="B29" s="1">
         <f t="shared" si="3"/>
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="C29">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D29" t="s">
         <v>38</v>
@@ -2767,47 +2737,41 @@
         <v>39</v>
       </c>
       <c r="G29" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="H29">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="I29">
         <v>1</v>
       </c>
       <c r="J29">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K29">
         <v>3</v>
       </c>
       <c r="L29">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="M29">
-        <v>30</v>
-      </c>
-      <c r="N29">
-        <v>60009</v>
-      </c>
-      <c r="O29" s="1">
-        <v>70010</v>
-      </c>
-      <c r="P29">
-        <v>201009</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16">
+        <v>0</v>
+      </c>
+      <c r="N29" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17">
       <c r="A30" s="1">
-        <f t="shared" si="2"/>
-        <v>100110</v>
+        <f t="shared" si="1"/>
+        <v>100205</v>
       </c>
       <c r="B30" s="1">
         <f t="shared" si="3"/>
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="C30">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D30" t="s">
         <v>38</v>
@@ -2819,59 +2783,53 @@
         <v>39</v>
       </c>
       <c r="G30" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="H30">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="I30">
         <v>1</v>
       </c>
       <c r="J30">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K30">
         <v>3</v>
       </c>
       <c r="L30">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="M30">
-        <v>30</v>
-      </c>
-      <c r="N30">
-        <v>60010</v>
-      </c>
-      <c r="O30" s="1">
-        <v>70010</v>
-      </c>
-      <c r="P30" t="s">
+        <v>0</v>
+      </c>
+      <c r="N30" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17">
+      <c r="A31" s="1">
+        <f t="shared" si="1"/>
+        <v>100206</v>
+      </c>
+      <c r="B31" s="1">
+        <f t="shared" si="3"/>
+        <v>1002</v>
+      </c>
+      <c r="C31">
+        <v>6</v>
+      </c>
+      <c r="D31" t="s">
+        <v>38</v>
+      </c>
+      <c r="E31" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" t="s">
+        <v>39</v>
+      </c>
+      <c r="G31" t="s">
         <v>40</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16">
-      <c r="A31" s="1">
-        <f t="shared" si="2"/>
-        <v>100200</v>
-      </c>
-      <c r="B31" s="1">
-        <f>B20+1</f>
-        <v>1002</v>
-      </c>
-      <c r="C31">
-        <v>0</v>
-      </c>
-      <c r="D31" t="s">
-        <v>41</v>
-      </c>
-      <c r="E31" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" t="s">
-        <v>42</v>
-      </c>
-      <c r="G31" t="s">
-        <v>43</v>
       </c>
       <c r="H31">
         <v>0</v>
@@ -2892,38 +2850,33 @@
         <v>0</v>
       </c>
       <c r="N31" t="s">
-        <v>21</v>
-      </c>
-      <c r="O31" t="s">
-        <v>21</v>
-      </c>
-      <c r="P31" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16">
+        <v>46</v>
+      </c>
+      <c r="Q31" s="1"/>
+    </row>
+    <row r="32" spans="1:17">
       <c r="A32" s="1">
-        <f t="shared" si="2"/>
-        <v>100201</v>
+        <f t="shared" si="1"/>
+        <v>100207</v>
       </c>
       <c r="B32" s="1">
-        <f t="shared" ref="B32:B41" si="4">B31</f>
+        <f t="shared" si="3"/>
         <v>1002</v>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D32" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E32" t="s">
         <v>21</v>
       </c>
       <c r="F32" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G32" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H32">
         <v>0</v>
@@ -2944,32 +2897,33 @@
         <v>0</v>
       </c>
       <c r="N32" t="s">
-        <v>44</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="Q32" s="1"/>
     </row>
     <row r="33" spans="1:17">
       <c r="A33" s="1">
-        <f t="shared" si="2"/>
-        <v>100202</v>
+        <f t="shared" si="1"/>
+        <v>100208</v>
       </c>
       <c r="B33" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1002</v>
       </c>
       <c r="C33">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D33" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E33" t="s">
         <v>21</v>
       </c>
       <c r="F33" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G33" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H33">
         <v>0</v>
@@ -2990,32 +2944,33 @@
         <v>0</v>
       </c>
       <c r="N33" t="s">
-        <v>45</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="Q33" s="1"/>
     </row>
     <row r="34" spans="1:17">
       <c r="A34" s="1">
-        <f t="shared" si="2"/>
-        <v>100203</v>
+        <f t="shared" si="1"/>
+        <v>100209</v>
       </c>
       <c r="B34" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1002</v>
       </c>
       <c r="C34">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D34" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E34" t="s">
         <v>21</v>
       </c>
       <c r="F34" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G34" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -3036,32 +2991,33 @@
         <v>0</v>
       </c>
       <c r="N34" t="s">
-        <v>46</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="Q34" s="1"/>
     </row>
     <row r="35" spans="1:17">
       <c r="A35" s="1">
-        <f t="shared" si="2"/>
-        <v>100204</v>
+        <f t="shared" si="1"/>
+        <v>100210</v>
       </c>
       <c r="B35" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1002</v>
       </c>
       <c r="C35">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D35" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E35" t="s">
         <v>21</v>
       </c>
       <c r="F35" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G35" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H35">
         <v>0</v>
@@ -3082,38 +3038,39 @@
         <v>0</v>
       </c>
       <c r="N35" t="s">
-        <v>47</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="Q35" s="1"/>
     </row>
     <row r="36" spans="1:17">
       <c r="A36" s="1">
-        <f t="shared" si="2"/>
-        <v>100205</v>
+        <f t="shared" si="1"/>
+        <v>100300</v>
       </c>
       <c r="B36" s="1">
-        <f t="shared" si="4"/>
-        <v>1002</v>
+        <f>B25+1</f>
+        <v>1003</v>
       </c>
       <c r="C36">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D36" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="E36" t="s">
         <v>21</v>
       </c>
       <c r="F36" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="G36" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="H36">
         <v>0</v>
       </c>
       <c r="I36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -3122,282 +3079,310 @@
         <v>3</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="M36">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N36" t="s">
-        <v>48</v>
+        <v>21</v>
+      </c>
+      <c r="O36" t="s">
+        <v>21</v>
+      </c>
+      <c r="P36" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="37" spans="1:17">
       <c r="A37" s="1">
-        <f t="shared" si="2"/>
-        <v>100206</v>
+        <f t="shared" si="1"/>
+        <v>100301</v>
       </c>
       <c r="B37" s="1">
-        <f t="shared" si="4"/>
-        <v>1002</v>
+        <f t="shared" ref="B37:B46" si="4">B36</f>
+        <v>1003</v>
       </c>
       <c r="C37">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D37" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="E37" t="s">
         <v>21</v>
       </c>
       <c r="F37" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="G37" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="I37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K37">
         <v>3</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="M37">
-        <v>0</v>
-      </c>
-      <c r="N37" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q37" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="N37">
+        <v>60011</v>
+      </c>
+      <c r="O37" s="1">
+        <v>70201</v>
+      </c>
+      <c r="P37" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="38" spans="1:17">
       <c r="A38" s="1">
-        <f t="shared" si="2"/>
-        <v>100207</v>
+        <f t="shared" si="1"/>
+        <v>100302</v>
       </c>
       <c r="B38" s="1">
         <f t="shared" si="4"/>
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="C38">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D38" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="E38" t="s">
         <v>21</v>
       </c>
       <c r="F38" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="G38" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="I38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K38">
         <v>3</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="M38">
-        <v>0</v>
-      </c>
-      <c r="N38" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q38" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="N38">
+        <v>60012</v>
+      </c>
+      <c r="O38" s="1">
+        <v>70201</v>
+      </c>
     </row>
     <row r="39" spans="1:17">
       <c r="A39" s="1">
-        <f t="shared" si="2"/>
-        <v>100208</v>
+        <f t="shared" si="1"/>
+        <v>100303</v>
       </c>
       <c r="B39" s="1">
         <f t="shared" si="4"/>
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="C39">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D39" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="E39" t="s">
         <v>21</v>
       </c>
       <c r="F39" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="G39" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="I39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J39">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K39">
         <v>3</v>
       </c>
       <c r="L39">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="M39">
-        <v>0</v>
-      </c>
-      <c r="N39" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q39" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="N39">
+        <v>60013</v>
+      </c>
+      <c r="O39" s="1">
+        <v>70201</v>
+      </c>
+      <c r="P39">
+        <v>201005</v>
+      </c>
     </row>
     <row r="40" spans="1:17">
       <c r="A40" s="1">
-        <f t="shared" si="2"/>
-        <v>100209</v>
+        <f t="shared" si="1"/>
+        <v>100304</v>
       </c>
       <c r="B40" s="1">
         <f t="shared" si="4"/>
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="C40">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D40" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="E40" t="s">
         <v>21</v>
       </c>
       <c r="F40" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="G40" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="I40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J40">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K40">
         <v>3</v>
       </c>
       <c r="L40">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="M40">
-        <v>0</v>
-      </c>
-      <c r="N40" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q40" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="N40">
+        <v>60014</v>
+      </c>
+      <c r="O40" s="1">
+        <v>70201</v>
+      </c>
+      <c r="P40">
+        <v>201005</v>
+      </c>
     </row>
     <row r="41" spans="1:17">
       <c r="A41" s="1">
-        <f t="shared" si="2"/>
-        <v>100210</v>
+        <f t="shared" si="1"/>
+        <v>100305</v>
       </c>
       <c r="B41" s="1">
         <f t="shared" si="4"/>
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="C41">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D41" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="E41" t="s">
         <v>21</v>
       </c>
       <c r="F41" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="G41" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="I41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J41">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K41">
         <v>3</v>
       </c>
       <c r="L41">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="M41">
-        <v>0</v>
-      </c>
-      <c r="N41" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q41" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="N41">
+        <v>60015</v>
+      </c>
+      <c r="O41" s="1">
+        <v>70204</v>
+      </c>
+      <c r="P41">
+        <v>201005</v>
+      </c>
     </row>
     <row r="42" spans="1:17">
       <c r="A42" s="1">
-        <f t="shared" si="2"/>
-        <v>100300</v>
+        <f t="shared" si="1"/>
+        <v>100306</v>
       </c>
       <c r="B42" s="1">
-        <f>B31+1</f>
+        <f t="shared" si="4"/>
         <v>1003</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D42" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E42" t="s">
         <v>21</v>
       </c>
       <c r="F42" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G42" t="s">
         <v>22</v>
       </c>
       <c r="H42">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I42">
         <v>2</v>
       </c>
       <c r="J42">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K42">
         <v>3</v>
@@ -3408,42 +3393,42 @@
       <c r="M42">
         <v>30</v>
       </c>
-      <c r="N42" t="s">
-        <v>21</v>
-      </c>
-      <c r="O42" t="s">
-        <v>21</v>
-      </c>
-      <c r="P42" t="s">
-        <v>21</v>
+      <c r="N42">
+        <v>60016</v>
+      </c>
+      <c r="O42" s="1">
+        <v>70204</v>
+      </c>
+      <c r="P42">
+        <v>201005</v>
       </c>
     </row>
     <row r="43" spans="1:17">
       <c r="A43" s="1">
-        <f t="shared" si="2"/>
-        <v>100301</v>
+        <f t="shared" si="1"/>
+        <v>100307</v>
       </c>
       <c r="B43" s="1">
-        <f t="shared" ref="B43:B52" si="5">B42</f>
+        <f t="shared" si="4"/>
         <v>1003</v>
       </c>
       <c r="C43">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D43" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E43" t="s">
         <v>21</v>
       </c>
       <c r="F43" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G43" t="s">
         <v>22</v>
       </c>
       <c r="H43">
-        <v>10000</v>
+        <v>16000</v>
       </c>
       <c r="I43">
         <v>2</v>
@@ -3461,41 +3446,41 @@
         <v>30</v>
       </c>
       <c r="N43">
-        <v>60011</v>
+        <v>60017</v>
       </c>
       <c r="O43" s="1">
-        <v>70200</v>
-      </c>
-      <c r="P43" t="s">
-        <v>21</v>
+        <v>70204</v>
+      </c>
+      <c r="P43">
+        <v>201005</v>
       </c>
     </row>
     <row r="44" spans="1:17">
       <c r="A44" s="1">
-        <f t="shared" si="2"/>
-        <v>100302</v>
+        <f t="shared" si="1"/>
+        <v>100308</v>
       </c>
       <c r="B44" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1003</v>
       </c>
       <c r="C44">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D44" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E44" t="s">
         <v>21</v>
       </c>
       <c r="F44" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G44" t="s">
         <v>22</v>
       </c>
       <c r="H44">
-        <v>10000</v>
+        <v>17000</v>
       </c>
       <c r="I44">
         <v>2</v>
@@ -3513,41 +3498,41 @@
         <v>30</v>
       </c>
       <c r="N44">
-        <v>60012</v>
+        <v>60018</v>
       </c>
       <c r="O44" s="1">
-        <v>70201</v>
-      </c>
-      <c r="P44">
-        <v>201002</v>
+        <v>70204</v>
+      </c>
+      <c r="P44" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="45" spans="1:17">
       <c r="A45" s="1">
-        <f t="shared" si="2"/>
-        <v>100303</v>
+        <f t="shared" si="1"/>
+        <v>100309</v>
       </c>
       <c r="B45" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1003</v>
       </c>
       <c r="C45">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D45" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E45" t="s">
         <v>21</v>
       </c>
       <c r="F45" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G45" t="s">
         <v>22</v>
       </c>
       <c r="H45">
-        <v>10000</v>
+        <v>18000</v>
       </c>
       <c r="I45">
         <v>2</v>
@@ -3565,41 +3550,41 @@
         <v>30</v>
       </c>
       <c r="N45">
-        <v>60013</v>
+        <v>60019</v>
       </c>
       <c r="O45" s="1">
-        <v>70202</v>
-      </c>
-      <c r="P45">
-        <v>201003</v>
+        <v>70204</v>
+      </c>
+      <c r="P45" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="46" spans="1:17">
       <c r="A46" s="1">
-        <f t="shared" si="2"/>
-        <v>100304</v>
+        <f t="shared" si="1"/>
+        <v>100310</v>
       </c>
       <c r="B46" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1003</v>
       </c>
       <c r="C46">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D46" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E46" t="s">
         <v>21</v>
       </c>
       <c r="F46" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G46" t="s">
         <v>22</v>
       </c>
       <c r="H46">
-        <v>10000</v>
+        <v>19000</v>
       </c>
       <c r="I46">
         <v>2</v>
@@ -3617,350 +3602,335 @@
         <v>30</v>
       </c>
       <c r="N46">
-        <v>60014</v>
+        <v>60020</v>
       </c>
       <c r="O46" s="1">
-        <v>70203</v>
-      </c>
-      <c r="P46">
-        <v>201004</v>
+        <v>70214</v>
+      </c>
+      <c r="P46" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="47" spans="1:17">
       <c r="A47" s="1">
-        <f t="shared" si="2"/>
-        <v>100305</v>
+        <f t="shared" si="1"/>
+        <v>100400</v>
       </c>
       <c r="B47" s="1">
-        <f t="shared" si="5"/>
-        <v>1003</v>
+        <f>B36+1</f>
+        <v>1004</v>
       </c>
       <c r="C47">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D47" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E47" t="s">
         <v>21</v>
       </c>
       <c r="F47" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G47" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="H47">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="I47">
         <v>2</v>
       </c>
       <c r="J47">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K47">
         <v>3</v>
       </c>
       <c r="L47">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="M47">
-        <v>30</v>
-      </c>
-      <c r="N47">
-        <v>60015</v>
-      </c>
-      <c r="O47" s="1">
-        <v>70204</v>
-      </c>
-      <c r="P47">
-        <v>201005</v>
+        <v>0</v>
+      </c>
+      <c r="N47" t="s">
+        <v>21</v>
+      </c>
+      <c r="O47" t="s">
+        <v>21</v>
+      </c>
+      <c r="P47" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="48" spans="1:17">
       <c r="A48" s="1">
-        <f t="shared" si="2"/>
-        <v>100306</v>
+        <f t="shared" si="1"/>
+        <v>100401</v>
       </c>
       <c r="B48" s="1">
-        <f t="shared" si="5"/>
-        <v>1003</v>
+        <f t="shared" ref="B48:B57" si="5">B47</f>
+        <v>1004</v>
       </c>
       <c r="C48">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D48" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E48" t="s">
         <v>21</v>
       </c>
       <c r="F48" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G48" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="H48">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="I48">
         <v>2</v>
       </c>
       <c r="J48">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K48">
         <v>3</v>
       </c>
       <c r="L48">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="M48">
-        <v>30</v>
-      </c>
-      <c r="N48">
-        <v>60016</v>
-      </c>
-      <c r="O48" s="1">
-        <v>70205</v>
+        <v>0</v>
+      </c>
+      <c r="N48" t="s">
+        <v>57</v>
       </c>
       <c r="P48" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
     </row>
     <row r="49" spans="1:16">
       <c r="A49" s="1">
-        <f t="shared" si="2"/>
-        <v>100307</v>
+        <f t="shared" si="1"/>
+        <v>100402</v>
       </c>
       <c r="B49" s="1">
         <f t="shared" si="5"/>
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="C49">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D49" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E49" t="s">
         <v>21</v>
       </c>
       <c r="F49" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G49" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="H49">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="I49">
         <v>2</v>
       </c>
       <c r="J49">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K49">
         <v>3</v>
       </c>
       <c r="L49">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="M49">
-        <v>30</v>
-      </c>
-      <c r="N49">
-        <v>60017</v>
-      </c>
-      <c r="O49" s="1">
-        <v>70206</v>
+        <v>0</v>
+      </c>
+      <c r="N49" t="s">
+        <v>58</v>
       </c>
       <c r="P49" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
     </row>
     <row r="50" spans="1:16">
       <c r="A50" s="1">
-        <f t="shared" si="2"/>
-        <v>100308</v>
+        <f t="shared" si="1"/>
+        <v>100403</v>
       </c>
       <c r="B50" s="1">
         <f t="shared" si="5"/>
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="C50">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D50" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E50" t="s">
         <v>21</v>
       </c>
       <c r="F50" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G50" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="H50">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="I50">
         <v>2</v>
       </c>
       <c r="J50">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K50">
         <v>3</v>
       </c>
       <c r="L50">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="M50">
-        <v>30</v>
-      </c>
-      <c r="N50">
-        <v>60018</v>
-      </c>
-      <c r="O50" s="1">
-        <v>70207</v>
+        <v>0</v>
+      </c>
+      <c r="N50" t="s">
+        <v>59</v>
       </c>
       <c r="P50" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
     </row>
     <row r="51" spans="1:16">
       <c r="A51" s="1">
-        <f t="shared" si="2"/>
-        <v>100309</v>
+        <f t="shared" si="1"/>
+        <v>100404</v>
       </c>
       <c r="B51" s="1">
         <f t="shared" si="5"/>
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="C51">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D51" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E51" t="s">
         <v>21</v>
       </c>
       <c r="F51" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G51" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="H51">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="I51">
         <v>2</v>
       </c>
       <c r="J51">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K51">
         <v>3</v>
       </c>
       <c r="L51">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="M51">
-        <v>30</v>
-      </c>
-      <c r="N51">
-        <v>60019</v>
-      </c>
-      <c r="O51" s="1">
-        <v>70208</v>
+        <v>0</v>
+      </c>
+      <c r="N51" t="s">
+        <v>60</v>
       </c>
       <c r="P51" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
     </row>
     <row r="52" spans="1:16">
       <c r="A52" s="1">
-        <f t="shared" si="2"/>
-        <v>100310</v>
+        <f t="shared" si="1"/>
+        <v>100405</v>
       </c>
       <c r="B52" s="1">
         <f t="shared" si="5"/>
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="C52">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D52" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E52" t="s">
         <v>21</v>
       </c>
       <c r="F52" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G52" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="H52">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="I52">
         <v>2</v>
       </c>
       <c r="J52">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K52">
         <v>3</v>
       </c>
       <c r="L52">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="M52">
-        <v>30</v>
-      </c>
-      <c r="N52">
-        <v>60020</v>
-      </c>
-      <c r="O52" s="1">
-        <v>70209</v>
+        <v>0</v>
+      </c>
+      <c r="N52" t="s">
+        <v>61</v>
       </c>
       <c r="P52" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
     </row>
     <row r="53" spans="1:16">
       <c r="A53" s="1">
-        <f t="shared" si="2"/>
-        <v>100400</v>
+        <f t="shared" si="1"/>
+        <v>100406</v>
       </c>
       <c r="B53" s="1">
-        <f>B42+1</f>
+        <f t="shared" si="5"/>
         <v>1004</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D53" t="s">
+        <v>55</v>
+      </c>
+      <c r="E53" t="s">
+        <v>21</v>
+      </c>
+      <c r="F53" t="s">
         <v>56</v>
       </c>
-      <c r="E53" t="s">
-        <v>21</v>
-      </c>
-      <c r="F53" t="s">
-        <v>57</v>
-      </c>
       <c r="G53" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H53">
         <v>0</v>
@@ -3981,10 +3951,7 @@
         <v>0</v>
       </c>
       <c r="N53" t="s">
-        <v>21</v>
-      </c>
-      <c r="O53" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="P53" t="s">
         <v>21</v>
@@ -3992,27 +3959,27 @@
     </row>
     <row r="54" spans="1:16">
       <c r="A54" s="1">
-        <f t="shared" si="2"/>
-        <v>100401</v>
+        <f t="shared" si="1"/>
+        <v>100407</v>
       </c>
       <c r="B54" s="1">
-        <f t="shared" ref="B54:B63" si="6">B53</f>
+        <f t="shared" si="5"/>
         <v>1004</v>
       </c>
       <c r="C54">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D54" t="s">
+        <v>55</v>
+      </c>
+      <c r="E54" t="s">
+        <v>21</v>
+      </c>
+      <c r="F54" t="s">
         <v>56</v>
       </c>
-      <c r="E54" t="s">
-        <v>21</v>
-      </c>
-      <c r="F54" t="s">
-        <v>57</v>
-      </c>
       <c r="G54" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H54">
         <v>0</v>
@@ -4033,7 +4000,7 @@
         <v>0</v>
       </c>
       <c r="N54" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="P54" t="s">
         <v>21</v>
@@ -4041,27 +4008,27 @@
     </row>
     <row r="55" spans="1:16">
       <c r="A55" s="1">
-        <f t="shared" si="2"/>
-        <v>100402</v>
+        <f t="shared" si="1"/>
+        <v>100408</v>
       </c>
       <c r="B55" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1004</v>
       </c>
       <c r="C55">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D55" t="s">
+        <v>55</v>
+      </c>
+      <c r="E55" t="s">
+        <v>21</v>
+      </c>
+      <c r="F55" t="s">
         <v>56</v>
       </c>
-      <c r="E55" t="s">
-        <v>21</v>
-      </c>
-      <c r="F55" t="s">
-        <v>57</v>
-      </c>
       <c r="G55" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H55">
         <v>0</v>
@@ -4082,7 +4049,7 @@
         <v>0</v>
       </c>
       <c r="N55" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="P55" t="s">
         <v>21</v>
@@ -4090,27 +4057,27 @@
     </row>
     <row r="56" spans="1:16">
       <c r="A56" s="1">
-        <f t="shared" si="2"/>
-        <v>100403</v>
+        <f t="shared" si="1"/>
+        <v>100409</v>
       </c>
       <c r="B56" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1004</v>
       </c>
       <c r="C56">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D56" t="s">
+        <v>55</v>
+      </c>
+      <c r="E56" t="s">
+        <v>21</v>
+      </c>
+      <c r="F56" t="s">
         <v>56</v>
       </c>
-      <c r="E56" t="s">
-        <v>21</v>
-      </c>
-      <c r="F56" t="s">
-        <v>57</v>
-      </c>
       <c r="G56" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H56">
         <v>0</v>
@@ -4131,7 +4098,7 @@
         <v>0</v>
       </c>
       <c r="N56" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="P56" t="s">
         <v>21</v>
@@ -4139,27 +4106,27 @@
     </row>
     <row r="57" spans="1:16">
       <c r="A57" s="1">
-        <f t="shared" si="2"/>
-        <v>100404</v>
+        <f t="shared" si="1"/>
+        <v>100410</v>
       </c>
       <c r="B57" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1004</v>
       </c>
       <c r="C57">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D57" t="s">
+        <v>55</v>
+      </c>
+      <c r="E57" t="s">
+        <v>21</v>
+      </c>
+      <c r="F57" t="s">
         <v>56</v>
       </c>
-      <c r="E57" t="s">
-        <v>21</v>
-      </c>
-      <c r="F57" t="s">
-        <v>57</v>
-      </c>
       <c r="G57" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H57">
         <v>0</v>
@@ -4180,7 +4147,7 @@
         <v>0</v>
       </c>
       <c r="N57" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="P57" t="s">
         <v>21</v>
@@ -4188,33 +4155,33 @@
     </row>
     <row r="58" spans="1:16">
       <c r="A58" s="1">
-        <f t="shared" si="2"/>
-        <v>100405</v>
+        <f t="shared" si="1"/>
+        <v>100500</v>
       </c>
       <c r="B58" s="1">
-        <f t="shared" si="6"/>
-        <v>1004</v>
+        <f>B47+1</f>
+        <v>1005</v>
       </c>
       <c r="C58">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D58" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E58" t="s">
         <v>21</v>
       </c>
       <c r="F58" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="G58" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="H58">
         <v>0</v>
       </c>
       <c r="I58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J58">
         <v>0</v>
@@ -4223,13 +4190,16 @@
         <v>3</v>
       </c>
       <c r="L58">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="M58">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N58" t="s">
-        <v>62</v>
+        <v>21</v>
+      </c>
+      <c r="O58" t="s">
+        <v>21</v>
       </c>
       <c r="P58" t="s">
         <v>21</v>
@@ -4237,281 +4207,296 @@
     </row>
     <row r="59" spans="1:16">
       <c r="A59" s="1">
-        <f t="shared" si="2"/>
-        <v>100406</v>
+        <f t="shared" si="1"/>
+        <v>100501</v>
       </c>
       <c r="B59" s="1">
-        <f t="shared" si="6"/>
-        <v>1004</v>
+        <f t="shared" ref="B59:B68" si="6">B58</f>
+        <v>1005</v>
       </c>
       <c r="C59">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D59" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E59" t="s">
         <v>21</v>
       </c>
       <c r="F59" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="G59" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="H59">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I59">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J59">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K59">
         <v>3</v>
       </c>
       <c r="L59">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="M59">
-        <v>0</v>
-      </c>
-      <c r="N59" t="s">
-        <v>63</v>
-      </c>
-      <c r="P59" t="s">
-        <v>21</v>
+        <v>30</v>
+      </c>
+      <c r="N59">
+        <v>60021</v>
+      </c>
+      <c r="O59" t="s">
+        <v>21</v>
+      </c>
+      <c r="P59">
+        <v>202001</v>
       </c>
     </row>
     <row r="60" spans="1:16">
       <c r="A60" s="1">
-        <f t="shared" si="2"/>
-        <v>100407</v>
+        <f t="shared" si="1"/>
+        <v>100502</v>
       </c>
       <c r="B60" s="1">
         <f t="shared" si="6"/>
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="C60">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D60" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E60" t="s">
         <v>21</v>
       </c>
       <c r="F60" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="G60" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="H60">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J60">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K60">
         <v>3</v>
       </c>
       <c r="L60">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="M60">
-        <v>0</v>
-      </c>
-      <c r="N60" t="s">
-        <v>64</v>
-      </c>
-      <c r="P60" t="s">
-        <v>21</v>
+        <v>30</v>
+      </c>
+      <c r="N60">
+        <v>60022</v>
+      </c>
+      <c r="O60" t="s">
+        <v>21</v>
+      </c>
+      <c r="P60">
+        <v>202001</v>
       </c>
     </row>
     <row r="61" spans="1:16">
       <c r="A61" s="1">
-        <f t="shared" si="2"/>
-        <v>100408</v>
+        <f t="shared" si="1"/>
+        <v>100503</v>
       </c>
       <c r="B61" s="1">
         <f t="shared" si="6"/>
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="C61">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D61" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E61" t="s">
         <v>21</v>
       </c>
       <c r="F61" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="G61" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="H61">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="I61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J61">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K61">
         <v>3</v>
       </c>
       <c r="L61">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="M61">
-        <v>0</v>
-      </c>
-      <c r="N61" t="s">
-        <v>65</v>
-      </c>
-      <c r="P61" t="s">
-        <v>21</v>
+        <v>30</v>
+      </c>
+      <c r="N61">
+        <v>60023</v>
+      </c>
+      <c r="O61" s="1">
+        <v>70300</v>
+      </c>
+      <c r="P61">
+        <v>202001</v>
       </c>
     </row>
     <row r="62" spans="1:16">
       <c r="A62" s="1">
-        <f t="shared" si="2"/>
-        <v>100409</v>
+        <f t="shared" si="1"/>
+        <v>100504</v>
       </c>
       <c r="B62" s="1">
         <f t="shared" si="6"/>
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="C62">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D62" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E62" t="s">
         <v>21</v>
       </c>
       <c r="F62" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="G62" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="H62">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="I62">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J62">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K62">
         <v>3</v>
       </c>
       <c r="L62">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="M62">
-        <v>0</v>
-      </c>
-      <c r="N62" t="s">
-        <v>66</v>
-      </c>
-      <c r="P62" t="s">
-        <v>21</v>
+        <v>30</v>
+      </c>
+      <c r="N62">
+        <v>60024</v>
+      </c>
+      <c r="O62" s="1">
+        <v>70300</v>
+      </c>
+      <c r="P62">
+        <v>202001</v>
       </c>
     </row>
     <row r="63" spans="1:16">
       <c r="A63" s="1">
-        <f t="shared" si="2"/>
-        <v>100410</v>
+        <f t="shared" si="1"/>
+        <v>100505</v>
       </c>
       <c r="B63" s="1">
         <f t="shared" si="6"/>
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="C63">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D63" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E63" t="s">
         <v>21</v>
       </c>
       <c r="F63" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="G63" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="H63">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="I63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J63">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K63">
         <v>3</v>
       </c>
       <c r="L63">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="M63">
-        <v>0</v>
-      </c>
-      <c r="N63" t="s">
-        <v>67</v>
-      </c>
-      <c r="P63" t="s">
-        <v>21</v>
+        <v>30</v>
+      </c>
+      <c r="N63">
+        <v>60025</v>
+      </c>
+      <c r="O63" s="1">
+        <v>70300</v>
+      </c>
+      <c r="P63">
+        <v>202002</v>
       </c>
     </row>
     <row r="64" spans="1:16">
       <c r="A64" s="1">
-        <f t="shared" si="2"/>
-        <v>100500</v>
+        <f t="shared" si="1"/>
+        <v>100506</v>
       </c>
       <c r="B64" s="1">
-        <f>B53+1</f>
+        <f t="shared" si="6"/>
         <v>1005</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D64" t="s">
+        <v>67</v>
+      </c>
+      <c r="E64" t="s">
+        <v>21</v>
+      </c>
+      <c r="F64" t="s">
         <v>68</v>
-      </c>
-      <c r="E64" t="s">
-        <v>21</v>
-      </c>
-      <c r="F64" t="s">
-        <v>69</v>
       </c>
       <c r="G64" t="s">
         <v>22</v>
       </c>
       <c r="H64">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="I64">
         <v>3</v>
       </c>
       <c r="J64">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K64">
         <v>3</v>
@@ -4522,42 +4507,42 @@
       <c r="M64">
         <v>30</v>
       </c>
-      <c r="N64" t="s">
-        <v>21</v>
-      </c>
-      <c r="O64" t="s">
-        <v>21</v>
-      </c>
-      <c r="P64" t="s">
-        <v>21</v>
+      <c r="N64">
+        <v>60026</v>
+      </c>
+      <c r="O64" s="1">
+        <v>70300</v>
+      </c>
+      <c r="P64">
+        <v>202002</v>
       </c>
     </row>
     <row r="65" spans="1:16">
       <c r="A65" s="1">
-        <f t="shared" si="2"/>
-        <v>100501</v>
+        <f t="shared" si="1"/>
+        <v>100507</v>
       </c>
       <c r="B65" s="1">
-        <f t="shared" ref="B65:B74" si="7">B64</f>
+        <f t="shared" si="6"/>
         <v>1005</v>
       </c>
       <c r="C65">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D65" t="s">
+        <v>67</v>
+      </c>
+      <c r="E65" t="s">
+        <v>21</v>
+      </c>
+      <c r="F65" t="s">
         <v>68</v>
-      </c>
-      <c r="E65" t="s">
-        <v>21</v>
-      </c>
-      <c r="F65" t="s">
-        <v>69</v>
       </c>
       <c r="G65" t="s">
         <v>22</v>
       </c>
       <c r="H65">
-        <v>10000</v>
+        <v>7000</v>
       </c>
       <c r="I65">
         <v>3</v>
@@ -4575,41 +4560,41 @@
         <v>30</v>
       </c>
       <c r="N65">
-        <v>60021</v>
-      </c>
-      <c r="O65" t="s">
-        <v>21</v>
+        <v>60027</v>
+      </c>
+      <c r="O65" s="1">
+        <v>70300</v>
       </c>
       <c r="P65">
-        <v>202001</v>
+        <v>202002</v>
       </c>
     </row>
     <row r="66" spans="1:16">
       <c r="A66" s="1">
-        <f t="shared" si="2"/>
-        <v>100502</v>
+        <f t="shared" si="1"/>
+        <v>100508</v>
       </c>
       <c r="B66" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1005</v>
       </c>
       <c r="C66">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D66" t="s">
+        <v>67</v>
+      </c>
+      <c r="E66" t="s">
+        <v>21</v>
+      </c>
+      <c r="F66" t="s">
         <v>68</v>
-      </c>
-      <c r="E66" t="s">
-        <v>21</v>
-      </c>
-      <c r="F66" t="s">
-        <v>69</v>
       </c>
       <c r="G66" t="s">
         <v>22</v>
       </c>
       <c r="H66">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="I66">
         <v>3</v>
@@ -4627,10 +4612,10 @@
         <v>30</v>
       </c>
       <c r="N66">
-        <v>60022</v>
-      </c>
-      <c r="O66" t="s">
-        <v>21</v>
+        <v>60028</v>
+      </c>
+      <c r="O66" s="1">
+        <v>70300</v>
       </c>
       <c r="P66">
         <v>202002</v>
@@ -4638,30 +4623,30 @@
     </row>
     <row r="67" spans="1:16">
       <c r="A67" s="1">
-        <f t="shared" si="2"/>
-        <v>100503</v>
+        <f t="shared" si="1"/>
+        <v>100509</v>
       </c>
       <c r="B67" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1005</v>
       </c>
       <c r="C67">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D67" t="s">
+        <v>67</v>
+      </c>
+      <c r="E67" t="s">
+        <v>21</v>
+      </c>
+      <c r="F67" t="s">
         <v>68</v>
-      </c>
-      <c r="E67" t="s">
-        <v>21</v>
-      </c>
-      <c r="F67" t="s">
-        <v>69</v>
       </c>
       <c r="G67" t="s">
         <v>22</v>
       </c>
       <c r="H67">
-        <v>10000</v>
+        <v>9000</v>
       </c>
       <c r="I67">
         <v>3</v>
@@ -4679,35 +4664,35 @@
         <v>30</v>
       </c>
       <c r="N67">
-        <v>60023</v>
-      </c>
-      <c r="O67" t="s">
-        <v>21</v>
+        <v>60029</v>
+      </c>
+      <c r="O67" s="1">
+        <v>70300</v>
       </c>
       <c r="P67">
-        <v>202003</v>
+        <v>202002</v>
       </c>
     </row>
     <row r="68" spans="1:16">
       <c r="A68" s="1">
-        <f t="shared" si="2"/>
-        <v>100504</v>
+        <f t="shared" si="1"/>
+        <v>100510</v>
       </c>
       <c r="B68" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1005</v>
       </c>
       <c r="C68">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D68" t="s">
+        <v>67</v>
+      </c>
+      <c r="E68" t="s">
+        <v>21</v>
+      </c>
+      <c r="F68" t="s">
         <v>68</v>
-      </c>
-      <c r="E68" t="s">
-        <v>21</v>
-      </c>
-      <c r="F68" t="s">
-        <v>69</v>
       </c>
       <c r="G68" t="s">
         <v>22</v>
@@ -4731,338 +4716,338 @@
         <v>30</v>
       </c>
       <c r="N68">
-        <v>60024</v>
-      </c>
-      <c r="O68" t="s">
-        <v>21</v>
-      </c>
-      <c r="P68">
-        <v>202004</v>
+        <v>60030</v>
+      </c>
+      <c r="O68" s="1">
+        <v>70300</v>
+      </c>
+      <c r="P68" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="69" spans="1:16">
       <c r="A69" s="1">
-        <f t="shared" si="2"/>
-        <v>100505</v>
+        <f t="shared" si="1"/>
+        <v>100600</v>
       </c>
       <c r="B69" s="1">
-        <f t="shared" si="7"/>
-        <v>1005</v>
+        <f>B58+1</f>
+        <v>1006</v>
       </c>
       <c r="C69">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D69" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E69" t="s">
         <v>21</v>
       </c>
       <c r="F69" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G69" t="s">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="H69">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="I69">
         <v>3</v>
       </c>
       <c r="J69">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K69">
         <v>3</v>
       </c>
       <c r="L69">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M69">
-        <v>30</v>
-      </c>
-      <c r="N69">
-        <v>60025</v>
+        <v>0</v>
+      </c>
+      <c r="N69" t="s">
+        <v>21</v>
       </c>
       <c r="O69" t="s">
         <v>21</v>
       </c>
-      <c r="P69">
-        <v>202005</v>
+      <c r="P69" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="70" spans="1:16">
       <c r="A70" s="1">
-        <f t="shared" si="2"/>
-        <v>100506</v>
+        <f t="shared" si="1"/>
+        <v>100601</v>
       </c>
       <c r="B70" s="1">
-        <f t="shared" si="7"/>
-        <v>1005</v>
+        <f t="shared" ref="B70:B79" si="7">B69</f>
+        <v>1006</v>
       </c>
       <c r="C70">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D70" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E70" t="s">
         <v>21</v>
       </c>
       <c r="F70" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G70" t="s">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="H70">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="I70">
         <v>3</v>
       </c>
       <c r="J70">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K70">
         <v>3</v>
       </c>
       <c r="L70">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M70">
-        <v>30</v>
-      </c>
-      <c r="N70">
-        <v>60026</v>
-      </c>
-      <c r="O70" s="1">
-        <v>70300</v>
-      </c>
-      <c r="P70">
-        <v>202006</v>
+        <v>0</v>
+      </c>
+      <c r="N70" t="s">
+        <v>73</v>
+      </c>
+      <c r="O70" t="s">
+        <v>21</v>
+      </c>
+      <c r="P70" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="71" spans="1:16">
       <c r="A71" s="1">
-        <f t="shared" si="2"/>
-        <v>100507</v>
+        <f t="shared" si="1"/>
+        <v>100602</v>
       </c>
       <c r="B71" s="1">
         <f t="shared" si="7"/>
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C71">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D71" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E71" t="s">
         <v>21</v>
       </c>
       <c r="F71" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G71" t="s">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="H71">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="I71">
         <v>3</v>
       </c>
       <c r="J71">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K71">
         <v>3</v>
       </c>
       <c r="L71">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M71">
-        <v>30</v>
-      </c>
-      <c r="N71">
-        <v>60027</v>
-      </c>
-      <c r="O71" s="1">
-        <v>70300</v>
-      </c>
-      <c r="P71">
-        <v>202007</v>
+        <v>0</v>
+      </c>
+      <c r="N71" t="s">
+        <v>74</v>
+      </c>
+      <c r="O71" t="s">
+        <v>21</v>
+      </c>
+      <c r="P71" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="72" spans="1:16">
       <c r="A72" s="1">
-        <f t="shared" si="2"/>
-        <v>100508</v>
+        <f t="shared" si="1"/>
+        <v>100603</v>
       </c>
       <c r="B72" s="1">
         <f t="shared" si="7"/>
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C72">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D72" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E72" t="s">
         <v>21</v>
       </c>
       <c r="F72" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G72" t="s">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="H72">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="I72">
         <v>3</v>
       </c>
       <c r="J72">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K72">
         <v>3</v>
       </c>
       <c r="L72">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M72">
-        <v>30</v>
-      </c>
-      <c r="N72">
-        <v>60028</v>
-      </c>
-      <c r="O72" s="1">
-        <v>70300</v>
-      </c>
-      <c r="P72">
-        <v>202008</v>
+        <v>0</v>
+      </c>
+      <c r="N72" t="s">
+        <v>75</v>
+      </c>
+      <c r="O72" t="s">
+        <v>21</v>
+      </c>
+      <c r="P72" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="73" spans="1:16">
       <c r="A73" s="1">
-        <f t="shared" si="2"/>
-        <v>100509</v>
+        <f t="shared" si="1"/>
+        <v>100604</v>
       </c>
       <c r="B73" s="1">
         <f t="shared" si="7"/>
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C73">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D73" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E73" t="s">
         <v>21</v>
       </c>
       <c r="F73" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G73" t="s">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="H73">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="I73">
         <v>3</v>
       </c>
       <c r="J73">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K73">
         <v>3</v>
       </c>
       <c r="L73">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M73">
-        <v>30</v>
-      </c>
-      <c r="N73">
-        <v>60029</v>
-      </c>
-      <c r="O73" s="1">
-        <v>70300</v>
-      </c>
-      <c r="P73">
-        <v>202009</v>
+        <v>0</v>
+      </c>
+      <c r="N73" t="s">
+        <v>76</v>
+      </c>
+      <c r="O73" t="s">
+        <v>21</v>
+      </c>
+      <c r="P73" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="74" spans="1:16">
       <c r="A74" s="1">
-        <f t="shared" si="2"/>
-        <v>100510</v>
+        <f t="shared" si="1"/>
+        <v>100605</v>
       </c>
       <c r="B74" s="1">
         <f t="shared" si="7"/>
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C74">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D74" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E74" t="s">
         <v>21</v>
       </c>
       <c r="F74" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G74" t="s">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="H74">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="I74">
         <v>3</v>
       </c>
       <c r="J74">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K74">
         <v>3</v>
       </c>
       <c r="L74">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M74">
-        <v>30</v>
-      </c>
-      <c r="N74">
-        <v>60030</v>
-      </c>
-      <c r="O74" s="1">
-        <v>70300</v>
-      </c>
-      <c r="P74">
-        <v>202010</v>
+        <v>0</v>
+      </c>
+      <c r="N74" t="s">
+        <v>77</v>
+      </c>
+      <c r="O74" t="s">
+        <v>21</v>
+      </c>
+      <c r="P74" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="75" spans="1:16">
       <c r="A75" s="1">
-        <f t="shared" si="2"/>
-        <v>100600</v>
+        <f t="shared" si="1"/>
+        <v>100606</v>
       </c>
       <c r="B75" s="1">
-        <f>B64+1</f>
+        <f t="shared" si="7"/>
         <v>1006</v>
       </c>
       <c r="C75">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D75" t="s">
         <v>70</v>
@@ -5095,26 +5080,23 @@
         <v>0</v>
       </c>
       <c r="N75" t="s">
-        <v>21</v>
+        <v>78</v>
       </c>
       <c r="O75" t="s">
-        <v>21</v>
-      </c>
-      <c r="P75" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="76" spans="1:16">
       <c r="A76" s="1">
-        <f t="shared" si="2"/>
-        <v>100601</v>
+        <f t="shared" si="1"/>
+        <v>100607</v>
       </c>
       <c r="B76" s="1">
-        <f t="shared" ref="B76:B85" si="8">B75</f>
+        <f t="shared" si="7"/>
         <v>1006</v>
       </c>
       <c r="C76">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D76" t="s">
         <v>70</v>
@@ -5147,26 +5129,23 @@
         <v>0</v>
       </c>
       <c r="N76" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="O76" t="s">
-        <v>21</v>
-      </c>
-      <c r="P76" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="77" spans="1:16">
       <c r="A77" s="1">
-        <f t="shared" si="2"/>
-        <v>100602</v>
+        <f t="shared" si="1"/>
+        <v>100608</v>
       </c>
       <c r="B77" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1006</v>
       </c>
       <c r="C77">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D77" t="s">
         <v>70</v>
@@ -5199,26 +5178,23 @@
         <v>0</v>
       </c>
       <c r="N77" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="O77" t="s">
-        <v>21</v>
-      </c>
-      <c r="P77" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="78" spans="1:16">
       <c r="A78" s="1">
-        <f t="shared" si="2"/>
-        <v>100603</v>
+        <f t="shared" ref="A78:A101" si="8">B78*100+C78</f>
+        <v>100609</v>
       </c>
       <c r="B78" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1006</v>
       </c>
       <c r="C78">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D78" t="s">
         <v>70</v>
@@ -5251,26 +5227,23 @@
         <v>0</v>
       </c>
       <c r="N78" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="O78" t="s">
-        <v>21</v>
-      </c>
-      <c r="P78" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="79" spans="1:16">
       <c r="A79" s="1">
-        <f t="shared" si="2"/>
-        <v>100604</v>
+        <f t="shared" si="8"/>
+        <v>100610</v>
       </c>
       <c r="B79" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1006</v>
       </c>
       <c r="C79">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D79" t="s">
         <v>70</v>
@@ -5303,44 +5276,38 @@
         <v>0</v>
       </c>
       <c r="N79" t="s">
-        <v>76</v>
-      </c>
-      <c r="O79" t="s">
-        <v>21</v>
-      </c>
-      <c r="P79" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
     </row>
     <row r="80" spans="1:16">
       <c r="A80" s="1">
-        <f t="shared" si="2"/>
-        <v>100605</v>
+        <f t="shared" si="8"/>
+        <v>100700</v>
       </c>
       <c r="B80" s="1">
-        <f t="shared" si="8"/>
-        <v>1006</v>
+        <f>B69+1</f>
+        <v>1007</v>
       </c>
       <c r="C80">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D80" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="E80" t="s">
         <v>21</v>
       </c>
       <c r="F80" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="G80" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="H80">
         <v>0</v>
       </c>
       <c r="I80">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J80">
         <v>0</v>
@@ -5349,13 +5316,13 @@
         <v>3</v>
       </c>
       <c r="L80">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="M80">
         <v>0</v>
       </c>
       <c r="N80" t="s">
-        <v>77</v>
+        <v>21</v>
       </c>
       <c r="O80" t="s">
         <v>21</v>
@@ -5366,33 +5333,33 @@
     </row>
     <row r="81" spans="1:16">
       <c r="A81" s="1">
-        <f t="shared" si="2"/>
-        <v>100606</v>
+        <f t="shared" si="8"/>
+        <v>100701</v>
       </c>
       <c r="B81" s="1">
-        <f t="shared" si="8"/>
-        <v>1006</v>
+        <f t="shared" ref="B81:B90" si="9">B80</f>
+        <v>1007</v>
       </c>
       <c r="C81">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D81" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="E81" t="s">
         <v>21</v>
       </c>
       <c r="F81" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="G81" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="H81">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="I81">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J81">
         <v>0</v>
@@ -5401,47 +5368,50 @@
         <v>3</v>
       </c>
       <c r="L81">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="M81">
         <v>0</v>
       </c>
-      <c r="N81" t="s">
-        <v>78</v>
-      </c>
-      <c r="O81" t="s">
+      <c r="N81">
+        <v>60031</v>
+      </c>
+      <c r="O81">
+        <v>40003</v>
+      </c>
+      <c r="P81" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="82" spans="1:16">
       <c r="A82" s="1">
-        <f t="shared" si="2"/>
-        <v>100607</v>
+        <f t="shared" si="8"/>
+        <v>100702</v>
       </c>
       <c r="B82" s="1">
-        <f t="shared" si="8"/>
-        <v>1006</v>
+        <f t="shared" si="9"/>
+        <v>1007</v>
       </c>
       <c r="C82">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D82" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="E82" t="s">
         <v>21</v>
       </c>
       <c r="F82" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="G82" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="H82">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="I82">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J82">
         <v>0</v>
@@ -5450,47 +5420,50 @@
         <v>3</v>
       </c>
       <c r="L82">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="M82">
         <v>0</v>
       </c>
-      <c r="N82" t="s">
-        <v>79</v>
-      </c>
-      <c r="O82" t="s">
+      <c r="N82">
+        <v>60032</v>
+      </c>
+      <c r="O82">
+        <v>40003</v>
+      </c>
+      <c r="P82" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="83" spans="1:16">
       <c r="A83" s="1">
-        <f t="shared" si="2"/>
-        <v>100608</v>
+        <f t="shared" si="8"/>
+        <v>100703</v>
       </c>
       <c r="B83" s="1">
-        <f t="shared" si="8"/>
-        <v>1006</v>
+        <f t="shared" si="9"/>
+        <v>1007</v>
       </c>
       <c r="C83">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D83" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="E83" t="s">
         <v>21</v>
       </c>
       <c r="F83" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="G83" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="H83">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="I83">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J83">
         <v>0</v>
@@ -5499,47 +5472,50 @@
         <v>3</v>
       </c>
       <c r="L83">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="M83">
         <v>0</v>
       </c>
-      <c r="N83" t="s">
-        <v>80</v>
+      <c r="N83">
+        <v>60033</v>
       </c>
       <c r="O83" t="s">
+        <v>85</v>
+      </c>
+      <c r="P83" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="84" spans="1:16">
       <c r="A84" s="1">
-        <f t="shared" ref="A84:A107" si="9">B84*100+C84</f>
-        <v>100609</v>
+        <f t="shared" si="8"/>
+        <v>100704</v>
       </c>
       <c r="B84" s="1">
-        <f t="shared" si="8"/>
-        <v>1006</v>
+        <f t="shared" si="9"/>
+        <v>1007</v>
       </c>
       <c r="C84">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D84" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="E84" t="s">
         <v>21</v>
       </c>
       <c r="F84" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="G84" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="H84">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="I84">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J84">
         <v>0</v>
@@ -5548,47 +5524,50 @@
         <v>3</v>
       </c>
       <c r="L84">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="M84">
         <v>0</v>
       </c>
-      <c r="N84" t="s">
-        <v>81</v>
+      <c r="N84">
+        <v>60034</v>
       </c>
       <c r="O84" t="s">
+        <v>85</v>
+      </c>
+      <c r="P84" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="85" spans="1:16">
       <c r="A85" s="1">
+        <f t="shared" si="8"/>
+        <v>100705</v>
+      </c>
+      <c r="B85" s="1">
         <f t="shared" si="9"/>
-        <v>100610</v>
-      </c>
-      <c r="B85" s="1">
-        <f t="shared" si="8"/>
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="C85">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D85" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="E85" t="s">
         <v>21</v>
       </c>
       <c r="F85" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="G85" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="H85">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="I85">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J85">
         <v>0</v>
@@ -5597,26 +5576,32 @@
         <v>3</v>
       </c>
       <c r="L85">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="M85">
         <v>0</v>
       </c>
-      <c r="N85" t="s">
-        <v>82</v>
+      <c r="N85">
+        <v>60035</v>
+      </c>
+      <c r="O85" t="s">
+        <v>85</v>
+      </c>
+      <c r="P85" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="86" spans="1:16">
       <c r="A86" s="1">
+        <f t="shared" si="8"/>
+        <v>100706</v>
+      </c>
+      <c r="B86" s="1">
         <f t="shared" si="9"/>
-        <v>100700</v>
-      </c>
-      <c r="B86" s="1">
-        <f>B75+1</f>
         <v>1007</v>
       </c>
       <c r="C86">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D86" t="s">
         <v>83</v>
@@ -5628,10 +5613,10 @@
         <v>84</v>
       </c>
       <c r="G86" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H86">
-        <v>0</v>
+        <v>5500</v>
       </c>
       <c r="I86">
         <v>4</v>
@@ -5648,11 +5633,11 @@
       <c r="M86">
         <v>0</v>
       </c>
-      <c r="N86" t="s">
-        <v>21</v>
+      <c r="N86">
+        <v>60036</v>
       </c>
       <c r="O86" t="s">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="P86" t="s">
         <v>21</v>
@@ -5660,15 +5645,15 @@
     </row>
     <row r="87" spans="1:16">
       <c r="A87" s="1">
+        <f t="shared" si="8"/>
+        <v>100707</v>
+      </c>
+      <c r="B87" s="1">
         <f t="shared" si="9"/>
-        <v>100701</v>
-      </c>
-      <c r="B87" s="1">
-        <f t="shared" ref="B87:B96" si="10">B86</f>
         <v>1007</v>
       </c>
       <c r="C87">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D87" t="s">
         <v>83</v>
@@ -5680,10 +5665,10 @@
         <v>84</v>
       </c>
       <c r="G87" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H87">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="I87">
         <v>4</v>
@@ -5701,10 +5686,10 @@
         <v>0</v>
       </c>
       <c r="N87">
-        <v>60031</v>
-      </c>
-      <c r="O87">
-        <v>40001</v>
+        <v>60037</v>
+      </c>
+      <c r="O87" t="s">
+        <v>85</v>
       </c>
       <c r="P87" t="s">
         <v>21</v>
@@ -5712,15 +5697,15 @@
     </row>
     <row r="88" spans="1:16">
       <c r="A88" s="1">
+        <f t="shared" si="8"/>
+        <v>100708</v>
+      </c>
+      <c r="B88" s="1">
         <f t="shared" si="9"/>
-        <v>100702</v>
-      </c>
-      <c r="B88" s="1">
-        <f t="shared" si="10"/>
         <v>1007</v>
       </c>
       <c r="C88">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D88" t="s">
         <v>83</v>
@@ -5732,10 +5717,10 @@
         <v>84</v>
       </c>
       <c r="G88" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H88">
-        <v>10000</v>
+        <v>6500</v>
       </c>
       <c r="I88">
         <v>4</v>
@@ -5753,10 +5738,10 @@
         <v>0</v>
       </c>
       <c r="N88">
-        <v>60032</v>
-      </c>
-      <c r="O88">
-        <v>40002</v>
+        <v>60038</v>
+      </c>
+      <c r="O88" t="s">
+        <v>86</v>
       </c>
       <c r="P88" t="s">
         <v>21</v>
@@ -5764,15 +5749,15 @@
     </row>
     <row r="89" spans="1:16">
       <c r="A89" s="1">
+        <f t="shared" si="8"/>
+        <v>100709</v>
+      </c>
+      <c r="B89" s="1">
         <f t="shared" si="9"/>
-        <v>100703</v>
-      </c>
-      <c r="B89" s="1">
-        <f t="shared" si="10"/>
         <v>1007</v>
       </c>
       <c r="C89">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D89" t="s">
         <v>83</v>
@@ -5784,10 +5769,10 @@
         <v>84</v>
       </c>
       <c r="G89" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H89">
-        <v>10000</v>
+        <v>7000</v>
       </c>
       <c r="I89">
         <v>4</v>
@@ -5805,10 +5790,10 @@
         <v>0</v>
       </c>
       <c r="N89">
-        <v>60033</v>
-      </c>
-      <c r="O89">
-        <v>40003</v>
+        <v>60039</v>
+      </c>
+      <c r="O89" t="s">
+        <v>86</v>
       </c>
       <c r="P89" t="s">
         <v>21</v>
@@ -5816,15 +5801,15 @@
     </row>
     <row r="90" spans="1:16">
       <c r="A90" s="1">
+        <f t="shared" si="8"/>
+        <v>100710</v>
+      </c>
+      <c r="B90" s="1">
         <f t="shared" si="9"/>
-        <v>100704</v>
-      </c>
-      <c r="B90" s="1">
-        <f t="shared" si="10"/>
         <v>1007</v>
       </c>
       <c r="C90">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D90" t="s">
         <v>83</v>
@@ -5836,10 +5821,10 @@
         <v>84</v>
       </c>
       <c r="G90" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H90">
-        <v>10000</v>
+        <v>7500</v>
       </c>
       <c r="I90">
         <v>4</v>
@@ -5856,11 +5841,11 @@
       <c r="M90">
         <v>0</v>
       </c>
-      <c r="N90">
-        <v>60034</v>
-      </c>
-      <c r="O90">
-        <v>40004</v>
+      <c r="N90" t="s">
+        <v>87</v>
+      </c>
+      <c r="O90" t="s">
+        <v>86</v>
       </c>
       <c r="P90" t="s">
         <v>21</v>
@@ -5868,30 +5853,30 @@
     </row>
     <row r="91" spans="1:16">
       <c r="A91" s="1">
-        <f t="shared" si="9"/>
-        <v>100705</v>
+        <f t="shared" si="8"/>
+        <v>100800</v>
       </c>
       <c r="B91" s="1">
-        <f t="shared" si="10"/>
-        <v>1007</v>
+        <f>B80+1</f>
+        <v>1008</v>
       </c>
       <c r="C91">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D91" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E91" t="s">
         <v>21</v>
       </c>
       <c r="F91" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="G91" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="H91">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="I91">
         <v>4</v>
@@ -5908,11 +5893,11 @@
       <c r="M91">
         <v>0</v>
       </c>
-      <c r="N91">
-        <v>60035</v>
-      </c>
-      <c r="O91">
-        <v>40005</v>
+      <c r="N91" t="s">
+        <v>21</v>
+      </c>
+      <c r="O91" t="s">
+        <v>21</v>
       </c>
       <c r="P91" t="s">
         <v>21</v>
@@ -5920,30 +5905,30 @@
     </row>
     <row r="92" spans="1:16">
       <c r="A92" s="1">
-        <f t="shared" si="9"/>
-        <v>100706</v>
+        <f t="shared" si="8"/>
+        <v>100801</v>
       </c>
       <c r="B92" s="1">
-        <f t="shared" si="10"/>
-        <v>1007</v>
+        <f t="shared" ref="B92:B101" si="10">B91</f>
+        <v>1008</v>
       </c>
       <c r="C92">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D92" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E92" t="s">
         <v>21</v>
       </c>
       <c r="F92" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="G92" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="H92">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="I92">
         <v>4</v>
@@ -5960,11 +5945,8 @@
       <c r="M92">
         <v>0</v>
       </c>
-      <c r="N92">
-        <v>60036</v>
-      </c>
-      <c r="O92" t="s">
-        <v>85</v>
+      <c r="N92" t="s">
+        <v>91</v>
       </c>
       <c r="P92" t="s">
         <v>21</v>
@@ -5972,30 +5954,30 @@
     </row>
     <row r="93" spans="1:16">
       <c r="A93" s="1">
-        <f t="shared" si="9"/>
-        <v>100707</v>
+        <f t="shared" si="8"/>
+        <v>100802</v>
       </c>
       <c r="B93" s="1">
         <f t="shared" si="10"/>
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="C93">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D93" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E93" t="s">
         <v>21</v>
       </c>
       <c r="F93" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="G93" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="H93">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="I93">
         <v>4</v>
@@ -6012,11 +5994,8 @@
       <c r="M93">
         <v>0</v>
       </c>
-      <c r="N93">
-        <v>60037</v>
-      </c>
-      <c r="O93" t="s">
-        <v>86</v>
+      <c r="N93" t="s">
+        <v>92</v>
       </c>
       <c r="P93" t="s">
         <v>21</v>
@@ -6024,30 +6003,30 @@
     </row>
     <row r="94" spans="1:16">
       <c r="A94" s="1">
-        <f t="shared" si="9"/>
-        <v>100708</v>
+        <f t="shared" si="8"/>
+        <v>100803</v>
       </c>
       <c r="B94" s="1">
         <f t="shared" si="10"/>
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="C94">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D94" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E94" t="s">
         <v>21</v>
       </c>
       <c r="F94" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="G94" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="H94">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="I94">
         <v>4</v>
@@ -6064,11 +6043,8 @@
       <c r="M94">
         <v>0</v>
       </c>
-      <c r="N94">
-        <v>60038</v>
-      </c>
-      <c r="O94" t="s">
-        <v>87</v>
+      <c r="N94" t="s">
+        <v>93</v>
       </c>
       <c r="P94" t="s">
         <v>21</v>
@@ -6076,30 +6052,30 @@
     </row>
     <row r="95" spans="1:16">
       <c r="A95" s="1">
-        <f t="shared" si="9"/>
-        <v>100709</v>
+        <f t="shared" si="8"/>
+        <v>100804</v>
       </c>
       <c r="B95" s="1">
         <f t="shared" si="10"/>
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="C95">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D95" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E95" t="s">
         <v>21</v>
       </c>
       <c r="F95" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="G95" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="H95">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="I95">
         <v>4</v>
@@ -6116,11 +6092,8 @@
       <c r="M95">
         <v>0</v>
       </c>
-      <c r="N95">
-        <v>60039</v>
-      </c>
-      <c r="O95" t="s">
-        <v>88</v>
+      <c r="N95" t="s">
+        <v>94</v>
       </c>
       <c r="P95" t="s">
         <v>21</v>
@@ -6128,30 +6101,30 @@
     </row>
     <row r="96" spans="1:16">
       <c r="A96" s="1">
-        <f t="shared" si="9"/>
-        <v>100710</v>
+        <f t="shared" si="8"/>
+        <v>100805</v>
       </c>
       <c r="B96" s="1">
         <f t="shared" si="10"/>
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="C96">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D96" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E96" t="s">
         <v>21</v>
       </c>
       <c r="F96" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="G96" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="H96">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="I96">
         <v>4</v>
@@ -6168,11 +6141,8 @@
       <c r="M96">
         <v>0</v>
       </c>
-      <c r="N96">
-        <v>60040</v>
-      </c>
-      <c r="O96" t="s">
-        <v>89</v>
+      <c r="N96" t="s">
+        <v>95</v>
       </c>
       <c r="P96" t="s">
         <v>21</v>
@@ -6180,27 +6150,27 @@
     </row>
     <row r="97" spans="1:16">
       <c r="A97" s="1">
-        <f t="shared" si="9"/>
-        <v>100800</v>
+        <f t="shared" si="8"/>
+        <v>100806</v>
       </c>
       <c r="B97" s="1">
-        <f>B86+1</f>
+        <f t="shared" si="10"/>
         <v>1008</v>
       </c>
       <c r="C97">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D97" t="s">
+        <v>88</v>
+      </c>
+      <c r="E97" t="s">
+        <v>21</v>
+      </c>
+      <c r="F97" t="s">
+        <v>89</v>
+      </c>
+      <c r="G97" t="s">
         <v>90</v>
-      </c>
-      <c r="E97" t="s">
-        <v>21</v>
-      </c>
-      <c r="F97" t="s">
-        <v>91</v>
-      </c>
-      <c r="G97" t="s">
-        <v>92</v>
       </c>
       <c r="H97">
         <v>0</v>
@@ -6221,10 +6191,7 @@
         <v>0</v>
       </c>
       <c r="N97" t="s">
-        <v>21</v>
-      </c>
-      <c r="O97" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="P97" t="s">
         <v>21</v>
@@ -6232,27 +6199,27 @@
     </row>
     <row r="98" spans="1:16">
       <c r="A98" s="1">
-        <f t="shared" si="9"/>
-        <v>100801</v>
+        <f t="shared" si="8"/>
+        <v>100807</v>
       </c>
       <c r="B98" s="1">
-        <f t="shared" ref="B98:B107" si="11">B97</f>
+        <f t="shared" si="10"/>
         <v>1008</v>
       </c>
       <c r="C98">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D98" t="s">
+        <v>88</v>
+      </c>
+      <c r="E98" t="s">
+        <v>21</v>
+      </c>
+      <c r="F98" t="s">
+        <v>89</v>
+      </c>
+      <c r="G98" t="s">
         <v>90</v>
-      </c>
-      <c r="E98" t="s">
-        <v>21</v>
-      </c>
-      <c r="F98" t="s">
-        <v>91</v>
-      </c>
-      <c r="G98" t="s">
-        <v>92</v>
       </c>
       <c r="H98">
         <v>0</v>
@@ -6273,7 +6240,7 @@
         <v>0</v>
       </c>
       <c r="N98" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="P98" t="s">
         <v>21</v>
@@ -6281,27 +6248,27 @@
     </row>
     <row r="99" spans="1:16">
       <c r="A99" s="1">
-        <f t="shared" si="9"/>
-        <v>100802</v>
+        <f t="shared" si="8"/>
+        <v>100808</v>
       </c>
       <c r="B99" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1008</v>
       </c>
       <c r="C99">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D99" t="s">
+        <v>88</v>
+      </c>
+      <c r="E99" t="s">
+        <v>21</v>
+      </c>
+      <c r="F99" t="s">
+        <v>89</v>
+      </c>
+      <c r="G99" t="s">
         <v>90</v>
-      </c>
-      <c r="E99" t="s">
-        <v>21</v>
-      </c>
-      <c r="F99" t="s">
-        <v>91</v>
-      </c>
-      <c r="G99" t="s">
-        <v>92</v>
       </c>
       <c r="H99">
         <v>0</v>
@@ -6322,7 +6289,7 @@
         <v>0</v>
       </c>
       <c r="N99" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="P99" t="s">
         <v>21</v>
@@ -6330,27 +6297,27 @@
     </row>
     <row r="100" spans="1:16">
       <c r="A100" s="1">
-        <f t="shared" si="9"/>
-        <v>100803</v>
+        <f t="shared" si="8"/>
+        <v>100809</v>
       </c>
       <c r="B100" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1008</v>
       </c>
       <c r="C100">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D100" t="s">
+        <v>88</v>
+      </c>
+      <c r="E100" t="s">
+        <v>21</v>
+      </c>
+      <c r="F100" t="s">
+        <v>89</v>
+      </c>
+      <c r="G100" t="s">
         <v>90</v>
-      </c>
-      <c r="E100" t="s">
-        <v>21</v>
-      </c>
-      <c r="F100" t="s">
-        <v>91</v>
-      </c>
-      <c r="G100" t="s">
-        <v>92</v>
       </c>
       <c r="H100">
         <v>0</v>
@@ -6371,7 +6338,7 @@
         <v>0</v>
       </c>
       <c r="N100" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="P100" t="s">
         <v>21</v>
@@ -6379,27 +6346,27 @@
     </row>
     <row r="101" spans="1:16">
       <c r="A101" s="1">
-        <f t="shared" si="9"/>
-        <v>100804</v>
+        <f t="shared" si="8"/>
+        <v>100810</v>
       </c>
       <c r="B101" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>1008</v>
       </c>
       <c r="C101">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D101" t="s">
+        <v>88</v>
+      </c>
+      <c r="E101" t="s">
+        <v>21</v>
+      </c>
+      <c r="F101" t="s">
+        <v>89</v>
+      </c>
+      <c r="G101" t="s">
         <v>90</v>
-      </c>
-      <c r="E101" t="s">
-        <v>21</v>
-      </c>
-      <c r="F101" t="s">
-        <v>91</v>
-      </c>
-      <c r="G101" t="s">
-        <v>92</v>
       </c>
       <c r="H101">
         <v>0</v>
@@ -6420,303 +6387,9 @@
         <v>0</v>
       </c>
       <c r="N101" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="P101" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="102" spans="1:16">
-      <c r="A102" s="1">
-        <f t="shared" si="9"/>
-        <v>100805</v>
-      </c>
-      <c r="B102" s="1">
-        <f t="shared" si="11"/>
-        <v>1008</v>
-      </c>
-      <c r="C102">
-        <v>5</v>
-      </c>
-      <c r="D102" t="s">
-        <v>90</v>
-      </c>
-      <c r="E102" t="s">
-        <v>21</v>
-      </c>
-      <c r="F102" t="s">
-        <v>91</v>
-      </c>
-      <c r="G102" t="s">
-        <v>92</v>
-      </c>
-      <c r="H102">
-        <v>0</v>
-      </c>
-      <c r="I102">
-        <v>4</v>
-      </c>
-      <c r="J102">
-        <v>0</v>
-      </c>
-      <c r="K102">
-        <v>3</v>
-      </c>
-      <c r="L102">
-        <v>0</v>
-      </c>
-      <c r="M102">
-        <v>0</v>
-      </c>
-      <c r="N102" t="s">
-        <v>97</v>
-      </c>
-      <c r="P102" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="103" spans="1:16">
-      <c r="A103" s="1">
-        <f t="shared" si="9"/>
-        <v>100806</v>
-      </c>
-      <c r="B103" s="1">
-        <f t="shared" si="11"/>
-        <v>1008</v>
-      </c>
-      <c r="C103">
-        <v>6</v>
-      </c>
-      <c r="D103" t="s">
-        <v>90</v>
-      </c>
-      <c r="E103" t="s">
-        <v>21</v>
-      </c>
-      <c r="F103" t="s">
-        <v>91</v>
-      </c>
-      <c r="G103" t="s">
-        <v>92</v>
-      </c>
-      <c r="H103">
-        <v>0</v>
-      </c>
-      <c r="I103">
-        <v>4</v>
-      </c>
-      <c r="J103">
-        <v>0</v>
-      </c>
-      <c r="K103">
-        <v>3</v>
-      </c>
-      <c r="L103">
-        <v>0</v>
-      </c>
-      <c r="M103">
-        <v>0</v>
-      </c>
-      <c r="N103" t="s">
-        <v>98</v>
-      </c>
-      <c r="P103" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="104" spans="1:16">
-      <c r="A104" s="1">
-        <f t="shared" si="9"/>
-        <v>100807</v>
-      </c>
-      <c r="B104" s="1">
-        <f t="shared" si="11"/>
-        <v>1008</v>
-      </c>
-      <c r="C104">
-        <v>7</v>
-      </c>
-      <c r="D104" t="s">
-        <v>90</v>
-      </c>
-      <c r="E104" t="s">
-        <v>21</v>
-      </c>
-      <c r="F104" t="s">
-        <v>91</v>
-      </c>
-      <c r="G104" t="s">
-        <v>92</v>
-      </c>
-      <c r="H104">
-        <v>0</v>
-      </c>
-      <c r="I104">
-        <v>4</v>
-      </c>
-      <c r="J104">
-        <v>0</v>
-      </c>
-      <c r="K104">
-        <v>3</v>
-      </c>
-      <c r="L104">
-        <v>0</v>
-      </c>
-      <c r="M104">
-        <v>0</v>
-      </c>
-      <c r="N104" t="s">
-        <v>99</v>
-      </c>
-      <c r="P104" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="105" spans="1:16">
-      <c r="A105" s="1">
-        <f t="shared" si="9"/>
-        <v>100808</v>
-      </c>
-      <c r="B105" s="1">
-        <f t="shared" si="11"/>
-        <v>1008</v>
-      </c>
-      <c r="C105">
-        <v>8</v>
-      </c>
-      <c r="D105" t="s">
-        <v>90</v>
-      </c>
-      <c r="E105" t="s">
-        <v>21</v>
-      </c>
-      <c r="F105" t="s">
-        <v>91</v>
-      </c>
-      <c r="G105" t="s">
-        <v>92</v>
-      </c>
-      <c r="H105">
-        <v>0</v>
-      </c>
-      <c r="I105">
-        <v>4</v>
-      </c>
-      <c r="J105">
-        <v>0</v>
-      </c>
-      <c r="K105">
-        <v>3</v>
-      </c>
-      <c r="L105">
-        <v>0</v>
-      </c>
-      <c r="M105">
-        <v>0</v>
-      </c>
-      <c r="N105" t="s">
-        <v>100</v>
-      </c>
-      <c r="P105" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="106" spans="1:16">
-      <c r="A106" s="1">
-        <f t="shared" si="9"/>
-        <v>100809</v>
-      </c>
-      <c r="B106" s="1">
-        <f t="shared" si="11"/>
-        <v>1008</v>
-      </c>
-      <c r="C106">
-        <v>9</v>
-      </c>
-      <c r="D106" t="s">
-        <v>90</v>
-      </c>
-      <c r="E106" t="s">
-        <v>21</v>
-      </c>
-      <c r="F106" t="s">
-        <v>91</v>
-      </c>
-      <c r="G106" t="s">
-        <v>92</v>
-      </c>
-      <c r="H106">
-        <v>0</v>
-      </c>
-      <c r="I106">
-        <v>4</v>
-      </c>
-      <c r="J106">
-        <v>0</v>
-      </c>
-      <c r="K106">
-        <v>3</v>
-      </c>
-      <c r="L106">
-        <v>0</v>
-      </c>
-      <c r="M106">
-        <v>0</v>
-      </c>
-      <c r="N106" t="s">
-        <v>101</v>
-      </c>
-      <c r="P106" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="107" spans="1:16">
-      <c r="A107" s="1">
-        <f t="shared" si="9"/>
-        <v>100810</v>
-      </c>
-      <c r="B107" s="1">
-        <f t="shared" si="11"/>
-        <v>1008</v>
-      </c>
-      <c r="C107">
-        <v>10</v>
-      </c>
-      <c r="D107" t="s">
-        <v>90</v>
-      </c>
-      <c r="E107" t="s">
-        <v>21</v>
-      </c>
-      <c r="F107" t="s">
-        <v>91</v>
-      </c>
-      <c r="G107" t="s">
-        <v>92</v>
-      </c>
-      <c r="H107">
-        <v>0</v>
-      </c>
-      <c r="I107">
-        <v>4</v>
-      </c>
-      <c r="J107">
-        <v>0</v>
-      </c>
-      <c r="K107">
-        <v>3</v>
-      </c>
-      <c r="L107">
-        <v>0</v>
-      </c>
-      <c r="M107">
-        <v>0</v>
-      </c>
-      <c r="N107" t="s">
-        <v>102</v>
-      </c>
-      <c r="P107" t="s">
         <v>21</v>
       </c>
     </row>
@@ -6734,7 +6407,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -6744,7 +6417,7 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/skill_config.xlsx
+++ b/Configs/skill_config.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="skill_config" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="103">
   <si>
     <t>id</t>
   </si>
@@ -1413,7 +1413,7 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="1">
-        <f t="shared" ref="A3:A7" si="0">B3*100+C3</f>
+        <f t="shared" ref="A3:A13" si="0">B3*100+C3</f>
         <v>1000001</v>
       </c>
       <c r="B3" s="1">
@@ -1662,7 +1662,7 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="1">
-        <f>B8*100+C8</f>
+        <f t="shared" si="0"/>
         <v>1000301</v>
       </c>
       <c r="B8" s="1">
@@ -1713,7 +1713,7 @@
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="1">
-        <f>B9*100+C9</f>
+        <f t="shared" si="0"/>
         <v>1000401</v>
       </c>
       <c r="B9" s="1">
@@ -1725,7 +1725,6 @@
       <c r="D9" t="s">
         <v>29</v>
       </c>
-      <c r="E9"/>
       <c r="G9" t="s">
         <v>30</v>
       </c>
@@ -1747,8 +1746,8 @@
       <c r="M9">
         <v>0</v>
       </c>
-      <c r="N9" t="s">
-        <v>21</v>
+      <c r="N9">
+        <v>110001</v>
       </c>
       <c r="O9">
         <v>40003</v>
@@ -1759,7 +1758,7 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="1">
-        <f>B10*100+C10</f>
+        <f t="shared" si="0"/>
         <v>2000001</v>
       </c>
       <c r="B10">
@@ -1810,7 +1809,7 @@
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="1">
-        <f>B11*100+C11</f>
+        <f t="shared" si="0"/>
         <v>1006101</v>
       </c>
       <c r="B11" s="1">
@@ -1861,7 +1860,7 @@
     </row>
     <row r="12" spans="1:16">
       <c r="A12" s="1">
-        <f>B12*100+C12</f>
+        <f t="shared" si="0"/>
         <v>1006102</v>
       </c>
       <c r="B12" s="1">
@@ -1912,7 +1911,7 @@
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="1">
-        <f>B13*100+C13</f>
+        <f t="shared" si="0"/>
         <v>1006103</v>
       </c>
       <c r="B13" s="1">
@@ -2064,7 +2063,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:15">
       <c r="A16" s="1">
         <f t="shared" si="1"/>
         <v>100102</v>
@@ -2113,7 +2112,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:17">
+    <row r="17" spans="1:16">
       <c r="A17" s="1">
         <f t="shared" si="1"/>
         <v>100103</v>
@@ -2165,7 +2164,7 @@
         <v>201004</v>
       </c>
     </row>
-    <row r="18" spans="1:17">
+    <row r="18" spans="1:16">
       <c r="A18" s="1">
         <f t="shared" si="1"/>
         <v>100104</v>
@@ -2217,7 +2216,7 @@
         <v>201004</v>
       </c>
     </row>
-    <row r="19" spans="1:17">
+    <row r="19" spans="1:16">
       <c r="A19" s="1">
         <f t="shared" si="1"/>
         <v>100105</v>
@@ -2269,7 +2268,7 @@
         <v>201008</v>
       </c>
     </row>
-    <row r="20" spans="1:17">
+    <row r="20" spans="1:16">
       <c r="A20" s="1">
         <f t="shared" si="1"/>
         <v>100106</v>
@@ -2319,7 +2318,7 @@
         <v>201008</v>
       </c>
     </row>
-    <row r="21" spans="1:17">
+    <row r="21" spans="1:16">
       <c r="A21" s="1">
         <f t="shared" si="1"/>
         <v>100107</v>
@@ -2369,7 +2368,7 @@
         <v>201008</v>
       </c>
     </row>
-    <row r="22" spans="1:17">
+    <row r="22" spans="1:16">
       <c r="A22" s="1">
         <f t="shared" si="1"/>
         <v>100108</v>
@@ -2421,7 +2420,7 @@
         <v>201008</v>
       </c>
     </row>
-    <row r="23" spans="1:17">
+    <row r="23" spans="1:16">
       <c r="A23" s="1">
         <f t="shared" si="1"/>
         <v>100109</v>
@@ -2473,7 +2472,7 @@
         <v>201008</v>
       </c>
     </row>
-    <row r="24" spans="1:17">
+    <row r="24" spans="1:16">
       <c r="A24" s="1">
         <f t="shared" si="1"/>
         <v>100110</v>
@@ -2525,7 +2524,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="25" spans="1:17">
+    <row r="25" spans="1:16">
       <c r="A25" s="1">
         <f t="shared" si="1"/>
         <v>100200</v>
@@ -2577,7 +2576,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:17">
+    <row r="26" spans="1:14">
       <c r="A26" s="1">
         <f t="shared" si="1"/>
         <v>100201</v>
@@ -2623,7 +2622,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="27" spans="1:17">
+    <row r="27" spans="1:14">
       <c r="A27" s="1">
         <f t="shared" si="1"/>
         <v>100202</v>
@@ -2669,7 +2668,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="28" spans="1:17">
+    <row r="28" spans="1:14">
       <c r="A28" s="1">
         <f t="shared" si="1"/>
         <v>100203</v>
@@ -2715,7 +2714,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="29" spans="1:17">
+    <row r="29" spans="1:14">
       <c r="A29" s="1">
         <f t="shared" si="1"/>
         <v>100204</v>
@@ -2761,7 +2760,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="30" spans="1:17">
+    <row r="30" spans="1:14">
       <c r="A30" s="1">
         <f t="shared" si="1"/>
         <v>100205</v>
@@ -3042,7 +3041,7 @@
       </c>
       <c r="Q35" s="1"/>
     </row>
-    <row r="36" spans="1:17">
+    <row r="36" spans="1:16">
       <c r="A36" s="1">
         <f t="shared" si="1"/>
         <v>100300</v>
@@ -3094,7 +3093,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="37" spans="1:17">
+    <row r="37" spans="1:16">
       <c r="A37" s="1">
         <f t="shared" si="1"/>
         <v>100301</v>
@@ -3146,7 +3145,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="38" spans="1:17">
+    <row r="38" spans="1:15">
       <c r="A38" s="1">
         <f t="shared" si="1"/>
         <v>100302</v>
@@ -3195,7 +3194,7 @@
         <v>70201</v>
       </c>
     </row>
-    <row r="39" spans="1:17">
+    <row r="39" spans="1:16">
       <c r="A39" s="1">
         <f t="shared" si="1"/>
         <v>100303</v>
@@ -3247,7 +3246,7 @@
         <v>201005</v>
       </c>
     </row>
-    <row r="40" spans="1:17">
+    <row r="40" spans="1:16">
       <c r="A40" s="1">
         <f t="shared" si="1"/>
         <v>100304</v>
@@ -3299,7 +3298,7 @@
         <v>201005</v>
       </c>
     </row>
-    <row r="41" spans="1:17">
+    <row r="41" spans="1:16">
       <c r="A41" s="1">
         <f t="shared" si="1"/>
         <v>100305</v>
@@ -3351,7 +3350,7 @@
         <v>201005</v>
       </c>
     </row>
-    <row r="42" spans="1:17">
+    <row r="42" spans="1:16">
       <c r="A42" s="1">
         <f t="shared" si="1"/>
         <v>100306</v>
@@ -3403,7 +3402,7 @@
         <v>201005</v>
       </c>
     </row>
-    <row r="43" spans="1:17">
+    <row r="43" spans="1:16">
       <c r="A43" s="1">
         <f t="shared" si="1"/>
         <v>100307</v>
@@ -3455,7 +3454,7 @@
         <v>201005</v>
       </c>
     </row>
-    <row r="44" spans="1:17">
+    <row r="44" spans="1:16">
       <c r="A44" s="1">
         <f t="shared" si="1"/>
         <v>100308</v>
@@ -3507,7 +3506,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="45" spans="1:17">
+    <row r="45" spans="1:16">
       <c r="A45" s="1">
         <f t="shared" si="1"/>
         <v>100309</v>
@@ -3559,7 +3558,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="46" spans="1:17">
+    <row r="46" spans="1:16">
       <c r="A46" s="1">
         <f t="shared" si="1"/>
         <v>100310</v>
@@ -3611,7 +3610,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="47" spans="1:17">
+    <row r="47" spans="1:16">
       <c r="A47" s="1">
         <f t="shared" si="1"/>
         <v>100400</v>
@@ -3663,7 +3662,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="48" spans="1:17">
+    <row r="48" spans="1:16">
       <c r="A48" s="1">
         <f t="shared" si="1"/>
         <v>100401</v>
@@ -5037,7 +5036,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="75" spans="1:16">
+    <row r="75" spans="1:15">
       <c r="A75" s="1">
         <f t="shared" si="1"/>
         <v>100606</v>
@@ -5086,7 +5085,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="76" spans="1:16">
+    <row r="76" spans="1:15">
       <c r="A76" s="1">
         <f t="shared" si="1"/>
         <v>100607</v>
@@ -5135,7 +5134,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="77" spans="1:16">
+    <row r="77" spans="1:15">
       <c r="A77" s="1">
         <f t="shared" si="1"/>
         <v>100608</v>
@@ -5184,7 +5183,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="78" spans="1:16">
+    <row r="78" spans="1:15">
       <c r="A78" s="1">
         <f t="shared" ref="A78:A101" si="8">B78*100+C78</f>
         <v>100609</v>
@@ -5233,7 +5232,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="79" spans="1:16">
+    <row r="79" spans="1:14">
       <c r="A79" s="1">
         <f t="shared" si="8"/>
         <v>100610</v>

--- a/Configs/skill_config.xlsx
+++ b/Configs/skill_config.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="skill_config" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="104">
   <si>
     <t>id</t>
   </si>
@@ -76,6 +76,9 @@
   </si>
   <si>
     <t>bulletEvents</t>
+  </si>
+  <si>
+    <t>eventEffect</t>
   </si>
   <si>
     <t>int</t>
@@ -1309,9 +1312,10 @@
     <col min="13" max="13" width="13.75" customWidth="1"/>
     <col min="14" max="14" width="26" customWidth="1"/>
     <col min="15" max="15" width="12.625" customWidth="1"/>
+    <col min="17" max="17" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:17">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1360,58 +1364,64 @@
       <c r="P1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" t="s">
         <v>17</v>
       </c>
-      <c r="E2" t="s">
+      <c r="I2" t="s">
         <v>17</v>
       </c>
-      <c r="F2" t="s">
+      <c r="J2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="s">
+      <c r="M2" t="s">
+        <v>19</v>
+      </c>
+      <c r="N2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q2" t="s">
         <v>17</v>
       </c>
-      <c r="H2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M2" t="s">
-        <v>18</v>
-      </c>
-      <c r="N2" t="s">
-        <v>19</v>
-      </c>
-      <c r="O2" t="s">
-        <v>19</v>
-      </c>
-      <c r="P2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16">
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3" s="1">
         <f t="shared" ref="A3:A13" si="0">B3*100+C3</f>
         <v>1000001</v>
@@ -1423,16 +1433,16 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H3">
         <v>10000</v>
@@ -1453,16 +1463,19 @@
         <v>10</v>
       </c>
       <c r="N3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P3">
         <v>204010</v>
       </c>
-    </row>
-    <row r="4" spans="1:16">
+      <c r="Q3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4" s="1">
         <f t="shared" si="0"/>
         <v>1000101</v>
@@ -1474,16 +1487,16 @@
         <v>1</v>
       </c>
       <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" t="s">
         <v>23</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" t="s">
-        <v>22</v>
       </c>
       <c r="H4">
         <v>10000</v>
@@ -1504,16 +1517,19 @@
         <v>50</v>
       </c>
       <c r="N4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16">
+        <v>22</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5" s="1">
         <f t="shared" si="0"/>
         <v>1000201</v>
@@ -1525,16 +1541,16 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H5">
         <v>10000</v>
@@ -1555,16 +1571,19 @@
         <v>50</v>
       </c>
       <c r="N5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16">
+        <v>22</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6" s="1">
         <f t="shared" si="0"/>
         <v>1000202</v>
@@ -1576,13 +1595,13 @@
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H6">
         <v>10000</v>
@@ -1603,16 +1622,19 @@
         <v>50</v>
       </c>
       <c r="N6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P6">
         <v>103000</v>
       </c>
-    </row>
-    <row r="7" customFormat="1" spans="1:16">
+      <c r="Q6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" spans="1:17">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
         <v>1000203</v>
@@ -1624,13 +1646,13 @@
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H7">
         <v>10000</v>
@@ -1651,16 +1673,19 @@
         <v>50</v>
       </c>
       <c r="N7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16">
+        <v>28</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>1000301</v>
@@ -1672,16 +1697,16 @@
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H8">
         <v>10000</v>
@@ -1702,16 +1727,19 @@
         <v>50</v>
       </c>
       <c r="N8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16">
+        <v>22</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>1000401</v>
@@ -1723,10 +1751,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H9">
         <v>3000</v>
@@ -1753,10 +1781,13 @@
         <v>40003</v>
       </c>
       <c r="P9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16">
+        <v>22</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>2000001</v>
@@ -1768,16 +1799,16 @@
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H10">
         <v>10000</v>
@@ -1798,16 +1829,19 @@
         <v>15</v>
       </c>
       <c r="N10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16">
+        <v>22</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
         <v>1006101</v>
@@ -1819,16 +1853,16 @@
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H11">
         <v>3000</v>
@@ -1849,16 +1883,19 @@
         <v>50</v>
       </c>
       <c r="N11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P11">
         <v>201003</v>
       </c>
-    </row>
-    <row r="12" spans="1:16">
+      <c r="Q11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
         <v>1006102</v>
@@ -1870,16 +1907,16 @@
         <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H12">
         <v>3000</v>
@@ -1900,16 +1937,19 @@
         <v>50</v>
       </c>
       <c r="N12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P12">
         <v>201010</v>
       </c>
-    </row>
-    <row r="13" spans="1:16">
+      <c r="Q12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
         <v>1006103</v>
@@ -1921,16 +1961,16 @@
         <v>3</v>
       </c>
       <c r="D13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H13">
         <v>3000</v>
@@ -1951,16 +1991,19 @@
         <v>50</v>
       </c>
       <c r="N13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P13" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16">
+        <v>35</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17">
       <c r="A14" s="1">
         <f t="shared" ref="A14:A77" si="1">B14*100+C14</f>
         <v>100100</v>
@@ -1972,16 +2015,16 @@
         <v>0</v>
       </c>
       <c r="D14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -2002,16 +2045,19 @@
         <v>30</v>
       </c>
       <c r="N14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16">
+        <v>22</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17">
       <c r="A15" s="1">
         <f t="shared" si="1"/>
         <v>100101</v>
@@ -2024,16 +2070,16 @@
         <v>1</v>
       </c>
       <c r="D15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H15">
         <v>10000</v>
@@ -2057,13 +2103,16 @@
         <v>60001</v>
       </c>
       <c r="O15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P15" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+        <v>22</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17">
       <c r="A16" s="1">
         <f t="shared" si="1"/>
         <v>100102</v>
@@ -2076,16 +2125,16 @@
         <v>2</v>
       </c>
       <c r="D16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H16">
         <v>11000</v>
@@ -2109,10 +2158,13 @@
         <v>60002</v>
       </c>
       <c r="O16" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16">
+        <v>22</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17">
       <c r="A17" s="1">
         <f t="shared" si="1"/>
         <v>100103</v>
@@ -2125,16 +2177,16 @@
         <v>3</v>
       </c>
       <c r="D17" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H17">
         <v>12000</v>
@@ -2158,13 +2210,16 @@
         <v>60003</v>
       </c>
       <c r="O17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P17">
         <v>201004</v>
       </c>
-    </row>
-    <row r="18" spans="1:16">
+      <c r="Q17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17">
       <c r="A18" s="1">
         <f t="shared" si="1"/>
         <v>100104</v>
@@ -2177,16 +2232,16 @@
         <v>4</v>
       </c>
       <c r="D18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H18">
         <v>13000</v>
@@ -2210,13 +2265,16 @@
         <v>60004</v>
       </c>
       <c r="O18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P18">
         <v>201004</v>
       </c>
-    </row>
-    <row r="19" spans="1:16">
+      <c r="Q18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17">
       <c r="A19" s="1">
         <f t="shared" si="1"/>
         <v>100105</v>
@@ -2229,16 +2287,16 @@
         <v>5</v>
       </c>
       <c r="D19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H19">
         <v>14000</v>
@@ -2262,13 +2320,16 @@
         <v>60005</v>
       </c>
       <c r="O19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P19">
         <v>201008</v>
       </c>
-    </row>
-    <row r="20" spans="1:16">
+      <c r="Q19" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17">
       <c r="A20" s="1">
         <f t="shared" si="1"/>
         <v>100106</v>
@@ -2281,16 +2342,16 @@
         <v>6</v>
       </c>
       <c r="D20" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H20">
         <v>15000</v>
@@ -2317,8 +2378,11 @@
       <c r="P20">
         <v>201008</v>
       </c>
-    </row>
-    <row r="21" spans="1:16">
+      <c r="Q20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17">
       <c r="A21" s="1">
         <f t="shared" si="1"/>
         <v>100107</v>
@@ -2331,16 +2395,16 @@
         <v>7</v>
       </c>
       <c r="D21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H21">
         <v>16000</v>
@@ -2367,8 +2431,11 @@
       <c r="P21">
         <v>201008</v>
       </c>
-    </row>
-    <row r="22" spans="1:16">
+      <c r="Q21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17">
       <c r="A22" s="1">
         <f t="shared" si="1"/>
         <v>100108</v>
@@ -2381,16 +2448,16 @@
         <v>8</v>
       </c>
       <c r="D22" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H22">
         <v>17000</v>
@@ -2419,8 +2486,11 @@
       <c r="P22">
         <v>201008</v>
       </c>
-    </row>
-    <row r="23" spans="1:16">
+      <c r="Q22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17">
       <c r="A23" s="1">
         <f t="shared" si="1"/>
         <v>100109</v>
@@ -2433,16 +2503,16 @@
         <v>9</v>
       </c>
       <c r="D23" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H23">
         <v>18000</v>
@@ -2471,8 +2541,11 @@
       <c r="P23">
         <v>201008</v>
       </c>
-    </row>
-    <row r="24" spans="1:16">
+      <c r="Q23" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17">
       <c r="A24" s="1">
         <f t="shared" si="1"/>
         <v>100110</v>
@@ -2485,16 +2558,16 @@
         <v>10</v>
       </c>
       <c r="D24" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G24" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H24">
         <v>19000</v>
@@ -2521,10 +2594,13 @@
         <v>70010</v>
       </c>
       <c r="P24" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16">
+        <v>38</v>
+      </c>
+      <c r="Q24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17">
       <c r="A25" s="1">
         <f t="shared" si="1"/>
         <v>100200</v>
@@ -2537,16 +2613,16 @@
         <v>0</v>
       </c>
       <c r="D25" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E25" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F25" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G25" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -2567,16 +2643,19 @@
         <v>0</v>
       </c>
       <c r="N25" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O25" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P25" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14">
+        <v>22</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17">
       <c r="A26" s="1">
         <f t="shared" si="1"/>
         <v>100201</v>
@@ -2589,16 +2668,16 @@
         <v>1</v>
       </c>
       <c r="D26" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E26" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F26" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G26" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -2619,10 +2698,13 @@
         <v>0</v>
       </c>
       <c r="N26" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14">
+        <v>42</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17">
       <c r="A27" s="1">
         <f t="shared" si="1"/>
         <v>100202</v>
@@ -2635,16 +2717,16 @@
         <v>2</v>
       </c>
       <c r="D27" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F27" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G27" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H27">
         <v>0</v>
@@ -2665,10 +2747,13 @@
         <v>0</v>
       </c>
       <c r="N27" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14">
+        <v>43</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17">
       <c r="A28" s="1">
         <f t="shared" si="1"/>
         <v>100203</v>
@@ -2681,16 +2766,16 @@
         <v>3</v>
       </c>
       <c r="D28" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E28" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F28" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G28" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H28">
         <v>0</v>
@@ -2711,10 +2796,13 @@
         <v>0</v>
       </c>
       <c r="N28" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14">
+        <v>44</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17">
       <c r="A29" s="1">
         <f t="shared" si="1"/>
         <v>100204</v>
@@ -2727,16 +2815,16 @@
         <v>4</v>
       </c>
       <c r="D29" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E29" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F29" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G29" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H29">
         <v>0</v>
@@ -2757,10 +2845,13 @@
         <v>0</v>
       </c>
       <c r="N29" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14">
+        <v>45</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17">
       <c r="A30" s="1">
         <f t="shared" si="1"/>
         <v>100205</v>
@@ -2773,16 +2864,16 @@
         <v>5</v>
       </c>
       <c r="D30" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E30" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F30" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G30" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H30">
         <v>0</v>
@@ -2803,7 +2894,10 @@
         <v>0</v>
       </c>
       <c r="N30" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="31" spans="1:17">
@@ -2819,16 +2913,16 @@
         <v>6</v>
       </c>
       <c r="D31" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E31" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F31" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G31" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H31">
         <v>0</v>
@@ -2849,9 +2943,11 @@
         <v>0</v>
       </c>
       <c r="N31" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q31" s="1"/>
+        <v>47</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="32" spans="1:17">
       <c r="A32" s="1">
@@ -2866,16 +2962,16 @@
         <v>7</v>
       </c>
       <c r="D32" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E32" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F32" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G32" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H32">
         <v>0</v>
@@ -2896,9 +2992,11 @@
         <v>0</v>
       </c>
       <c r="N32" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q32" s="1"/>
+        <v>48</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="33" spans="1:17">
       <c r="A33" s="1">
@@ -2913,16 +3011,16 @@
         <v>8</v>
       </c>
       <c r="D33" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E33" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F33" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G33" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H33">
         <v>0</v>
@@ -2943,9 +3041,11 @@
         <v>0</v>
       </c>
       <c r="N33" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q33" s="1"/>
+        <v>49</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="34" spans="1:17">
       <c r="A34" s="1">
@@ -2960,16 +3060,16 @@
         <v>9</v>
       </c>
       <c r="D34" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E34" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F34" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G34" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -2990,9 +3090,11 @@
         <v>0</v>
       </c>
       <c r="N34" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q34" s="1"/>
+        <v>50</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="35" spans="1:17">
       <c r="A35" s="1">
@@ -3007,16 +3109,16 @@
         <v>10</v>
       </c>
       <c r="D35" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F35" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G35" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H35">
         <v>0</v>
@@ -3037,11 +3139,13 @@
         <v>0</v>
       </c>
       <c r="N35" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q35" s="1"/>
-    </row>
-    <row r="36" spans="1:16">
+        <v>51</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17">
       <c r="A36" s="1">
         <f t="shared" si="1"/>
         <v>100300</v>
@@ -3054,16 +3158,16 @@
         <v>0</v>
       </c>
       <c r="D36" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F36" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G36" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H36">
         <v>0</v>
@@ -3084,16 +3188,16 @@
         <v>30</v>
       </c>
       <c r="N36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P36" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17">
       <c r="A37" s="1">
         <f t="shared" si="1"/>
         <v>100301</v>
@@ -3106,16 +3210,16 @@
         <v>1</v>
       </c>
       <c r="D37" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E37" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F37" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G37" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H37">
         <v>10000</v>
@@ -3142,10 +3246,10 @@
         <v>70201</v>
       </c>
       <c r="P37" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17">
       <c r="A38" s="1">
         <f t="shared" si="1"/>
         <v>100302</v>
@@ -3158,16 +3262,16 @@
         <v>2</v>
       </c>
       <c r="D38" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E38" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G38" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H38">
         <v>11000</v>
@@ -3194,7 +3298,7 @@
         <v>70201</v>
       </c>
     </row>
-    <row r="39" spans="1:16">
+    <row r="39" spans="1:17">
       <c r="A39" s="1">
         <f t="shared" si="1"/>
         <v>100303</v>
@@ -3207,16 +3311,16 @@
         <v>3</v>
       </c>
       <c r="D39" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F39" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G39" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H39">
         <v>12000</v>
@@ -3246,7 +3350,7 @@
         <v>201005</v>
       </c>
     </row>
-    <row r="40" spans="1:16">
+    <row r="40" spans="1:17">
       <c r="A40" s="1">
         <f t="shared" si="1"/>
         <v>100304</v>
@@ -3259,16 +3363,16 @@
         <v>4</v>
       </c>
       <c r="D40" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E40" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F40" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G40" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H40">
         <v>13000</v>
@@ -3298,7 +3402,7 @@
         <v>201005</v>
       </c>
     </row>
-    <row r="41" spans="1:16">
+    <row r="41" spans="1:17">
       <c r="A41" s="1">
         <f t="shared" si="1"/>
         <v>100305</v>
@@ -3311,16 +3415,16 @@
         <v>5</v>
       </c>
       <c r="D41" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E41" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F41" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G41" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H41">
         <v>14000</v>
@@ -3350,7 +3454,7 @@
         <v>201005</v>
       </c>
     </row>
-    <row r="42" spans="1:16">
+    <row r="42" spans="1:17">
       <c r="A42" s="1">
         <f t="shared" si="1"/>
         <v>100306</v>
@@ -3363,16 +3467,16 @@
         <v>6</v>
       </c>
       <c r="D42" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E42" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F42" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G42" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H42">
         <v>15000</v>
@@ -3402,7 +3506,7 @@
         <v>201005</v>
       </c>
     </row>
-    <row r="43" spans="1:16">
+    <row r="43" spans="1:17">
       <c r="A43" s="1">
         <f t="shared" si="1"/>
         <v>100307</v>
@@ -3415,16 +3519,16 @@
         <v>7</v>
       </c>
       <c r="D43" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E43" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F43" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G43" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H43">
         <v>16000</v>
@@ -3454,7 +3558,7 @@
         <v>201005</v>
       </c>
     </row>
-    <row r="44" spans="1:16">
+    <row r="44" spans="1:17">
       <c r="A44" s="1">
         <f t="shared" si="1"/>
         <v>100308</v>
@@ -3467,16 +3571,16 @@
         <v>8</v>
       </c>
       <c r="D44" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E44" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F44" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G44" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H44">
         <v>17000</v>
@@ -3503,10 +3607,10 @@
         <v>70204</v>
       </c>
       <c r="P44" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17">
       <c r="A45" s="1">
         <f t="shared" si="1"/>
         <v>100309</v>
@@ -3519,16 +3623,16 @@
         <v>9</v>
       </c>
       <c r="D45" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E45" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F45" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G45" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H45">
         <v>18000</v>
@@ -3555,10 +3659,10 @@
         <v>70204</v>
       </c>
       <c r="P45" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17">
       <c r="A46" s="1">
         <f t="shared" si="1"/>
         <v>100310</v>
@@ -3571,16 +3675,16 @@
         <v>10</v>
       </c>
       <c r="D46" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E46" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F46" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G46" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H46">
         <v>19000</v>
@@ -3607,10 +3711,10 @@
         <v>70214</v>
       </c>
       <c r="P46" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17">
       <c r="A47" s="1">
         <f t="shared" si="1"/>
         <v>100400</v>
@@ -3623,16 +3727,16 @@
         <v>0</v>
       </c>
       <c r="D47" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E47" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F47" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G47" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H47">
         <v>0</v>
@@ -3653,16 +3757,16 @@
         <v>0</v>
       </c>
       <c r="N47" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O47" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P47" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17">
       <c r="A48" s="1">
         <f t="shared" si="1"/>
         <v>100401</v>
@@ -3675,16 +3779,16 @@
         <v>1</v>
       </c>
       <c r="D48" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E48" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F48" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G48" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H48">
         <v>0</v>
@@ -3705,10 +3809,10 @@
         <v>0</v>
       </c>
       <c r="N48" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P48" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3724,16 +3828,16 @@
         <v>2</v>
       </c>
       <c r="D49" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E49" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F49" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G49" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H49">
         <v>0</v>
@@ -3754,10 +3858,10 @@
         <v>0</v>
       </c>
       <c r="N49" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P49" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3773,16 +3877,16 @@
         <v>3</v>
       </c>
       <c r="D50" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E50" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F50" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G50" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H50">
         <v>0</v>
@@ -3803,10 +3907,10 @@
         <v>0</v>
       </c>
       <c r="N50" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P50" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -3822,16 +3926,16 @@
         <v>4</v>
       </c>
       <c r="D51" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E51" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F51" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G51" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H51">
         <v>0</v>
@@ -3852,10 +3956,10 @@
         <v>0</v>
       </c>
       <c r="N51" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P51" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -3871,16 +3975,16 @@
         <v>5</v>
       </c>
       <c r="D52" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E52" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F52" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G52" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H52">
         <v>0</v>
@@ -3901,10 +4005,10 @@
         <v>0</v>
       </c>
       <c r="N52" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P52" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -3920,16 +4024,16 @@
         <v>6</v>
       </c>
       <c r="D53" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E53" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F53" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G53" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H53">
         <v>0</v>
@@ -3950,10 +4054,10 @@
         <v>0</v>
       </c>
       <c r="N53" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P53" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -3969,16 +4073,16 @@
         <v>7</v>
       </c>
       <c r="D54" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E54" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F54" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G54" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H54">
         <v>0</v>
@@ -3999,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="N54" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P54" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4018,16 +4122,16 @@
         <v>8</v>
       </c>
       <c r="D55" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E55" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F55" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G55" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H55">
         <v>0</v>
@@ -4048,10 +4152,10 @@
         <v>0</v>
       </c>
       <c r="N55" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P55" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4067,16 +4171,16 @@
         <v>9</v>
       </c>
       <c r="D56" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E56" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F56" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G56" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H56">
         <v>0</v>
@@ -4097,10 +4201,10 @@
         <v>0</v>
       </c>
       <c r="N56" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P56" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4116,16 +4220,16 @@
         <v>10</v>
       </c>
       <c r="D57" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E57" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F57" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G57" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H57">
         <v>0</v>
@@ -4146,10 +4250,10 @@
         <v>0</v>
       </c>
       <c r="N57" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="P57" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4165,16 +4269,16 @@
         <v>0</v>
       </c>
       <c r="D58" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E58" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F58" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G58" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H58">
         <v>0</v>
@@ -4195,13 +4299,13 @@
         <v>30</v>
       </c>
       <c r="N58" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O58" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P58" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4217,16 +4321,16 @@
         <v>1</v>
       </c>
       <c r="D59" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E59" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F59" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G59" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H59">
         <v>1000</v>
@@ -4250,7 +4354,7 @@
         <v>60021</v>
       </c>
       <c r="O59" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P59">
         <v>202001</v>
@@ -4269,16 +4373,16 @@
         <v>2</v>
       </c>
       <c r="D60" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E60" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F60" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G60" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H60">
         <v>2000</v>
@@ -4302,7 +4406,7 @@
         <v>60022</v>
       </c>
       <c r="O60" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P60">
         <v>202001</v>
@@ -4321,16 +4425,16 @@
         <v>3</v>
       </c>
       <c r="D61" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E61" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F61" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G61" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H61">
         <v>3000</v>
@@ -4373,16 +4477,16 @@
         <v>4</v>
       </c>
       <c r="D62" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E62" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F62" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G62" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H62">
         <v>4000</v>
@@ -4425,16 +4529,16 @@
         <v>5</v>
       </c>
       <c r="D63" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E63" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F63" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G63" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H63">
         <v>5000</v>
@@ -4477,16 +4581,16 @@
         <v>6</v>
       </c>
       <c r="D64" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E64" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F64" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G64" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H64">
         <v>6000</v>
@@ -4516,7 +4620,7 @@
         <v>202002</v>
       </c>
     </row>
-    <row r="65" spans="1:16">
+    <row r="65" spans="1:17">
       <c r="A65" s="1">
         <f t="shared" si="1"/>
         <v>100507</v>
@@ -4529,16 +4633,16 @@
         <v>7</v>
       </c>
       <c r="D65" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E65" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F65" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G65" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H65">
         <v>7000</v>
@@ -4568,7 +4672,7 @@
         <v>202002</v>
       </c>
     </row>
-    <row r="66" spans="1:16">
+    <row r="66" spans="1:17">
       <c r="A66" s="1">
         <f t="shared" si="1"/>
         <v>100508</v>
@@ -4581,16 +4685,16 @@
         <v>8</v>
       </c>
       <c r="D66" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E66" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F66" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G66" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H66">
         <v>8000</v>
@@ -4620,7 +4724,7 @@
         <v>202002</v>
       </c>
     </row>
-    <row r="67" spans="1:16">
+    <row r="67" spans="1:17">
       <c r="A67" s="1">
         <f t="shared" si="1"/>
         <v>100509</v>
@@ -4633,16 +4737,16 @@
         <v>9</v>
       </c>
       <c r="D67" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E67" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F67" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G67" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H67">
         <v>9000</v>
@@ -4672,7 +4776,7 @@
         <v>202002</v>
       </c>
     </row>
-    <row r="68" spans="1:16">
+    <row r="68" spans="1:17">
       <c r="A68" s="1">
         <f t="shared" si="1"/>
         <v>100510</v>
@@ -4685,16 +4789,16 @@
         <v>10</v>
       </c>
       <c r="D68" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E68" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F68" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G68" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H68">
         <v>10000</v>
@@ -4721,10 +4825,13 @@
         <v>70300</v>
       </c>
       <c r="P68" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="69" spans="1:16">
+        <v>70</v>
+      </c>
+      <c r="Q68">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17">
       <c r="A69" s="1">
         <f t="shared" si="1"/>
         <v>100600</v>
@@ -4737,16 +4844,16 @@
         <v>0</v>
       </c>
       <c r="D69" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E69" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F69" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G69" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H69">
         <v>0</v>
@@ -4767,16 +4874,16 @@
         <v>0</v>
       </c>
       <c r="N69" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O69" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P69" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="70" spans="1:16">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17">
       <c r="A70" s="1">
         <f t="shared" si="1"/>
         <v>100601</v>
@@ -4789,16 +4896,16 @@
         <v>1</v>
       </c>
       <c r="D70" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E70" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F70" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G70" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H70">
         <v>0</v>
@@ -4819,16 +4926,16 @@
         <v>0</v>
       </c>
       <c r="N70" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O70" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P70" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17">
       <c r="A71" s="1">
         <f t="shared" si="1"/>
         <v>100602</v>
@@ -4841,16 +4948,16 @@
         <v>2</v>
       </c>
       <c r="D71" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E71" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F71" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G71" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H71">
         <v>0</v>
@@ -4871,16 +4978,16 @@
         <v>0</v>
       </c>
       <c r="N71" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O71" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P71" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="72" spans="1:16">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17">
       <c r="A72" s="1">
         <f t="shared" si="1"/>
         <v>100603</v>
@@ -4893,16 +5000,16 @@
         <v>3</v>
       </c>
       <c r="D72" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E72" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F72" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G72" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H72">
         <v>0</v>
@@ -4923,16 +5030,16 @@
         <v>0</v>
       </c>
       <c r="N72" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O72" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P72" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="73" spans="1:16">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17">
       <c r="A73" s="1">
         <f t="shared" si="1"/>
         <v>100604</v>
@@ -4945,16 +5052,16 @@
         <v>4</v>
       </c>
       <c r="D73" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E73" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F73" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G73" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H73">
         <v>0</v>
@@ -4975,16 +5082,16 @@
         <v>0</v>
       </c>
       <c r="N73" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O73" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P73" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="74" spans="1:16">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17">
       <c r="A74" s="1">
         <f t="shared" si="1"/>
         <v>100605</v>
@@ -4997,16 +5104,16 @@
         <v>5</v>
       </c>
       <c r="D74" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E74" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F74" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G74" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H74">
         <v>0</v>
@@ -5027,16 +5134,16 @@
         <v>0</v>
       </c>
       <c r="N74" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O74" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P74" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="75" spans="1:15">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17">
       <c r="A75" s="1">
         <f t="shared" si="1"/>
         <v>100606</v>
@@ -5049,16 +5156,16 @@
         <v>6</v>
       </c>
       <c r="D75" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E75" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F75" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G75" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H75">
         <v>0</v>
@@ -5079,13 +5186,13 @@
         <v>0</v>
       </c>
       <c r="N75" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O75" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="76" spans="1:15">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17">
       <c r="A76" s="1">
         <f t="shared" si="1"/>
         <v>100607</v>
@@ -5098,16 +5205,16 @@
         <v>7</v>
       </c>
       <c r="D76" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E76" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F76" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G76" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H76">
         <v>0</v>
@@ -5128,13 +5235,13 @@
         <v>0</v>
       </c>
       <c r="N76" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O76" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="77" spans="1:15">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17">
       <c r="A77" s="1">
         <f t="shared" si="1"/>
         <v>100608</v>
@@ -5147,16 +5254,16 @@
         <v>8</v>
       </c>
       <c r="D77" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E77" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F77" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G77" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H77">
         <v>0</v>
@@ -5177,13 +5284,13 @@
         <v>0</v>
       </c>
       <c r="N77" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O77" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="78" spans="1:15">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17">
       <c r="A78" s="1">
         <f t="shared" ref="A78:A101" si="8">B78*100+C78</f>
         <v>100609</v>
@@ -5196,16 +5303,16 @@
         <v>9</v>
       </c>
       <c r="D78" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E78" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F78" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G78" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H78">
         <v>0</v>
@@ -5226,13 +5333,13 @@
         <v>0</v>
       </c>
       <c r="N78" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O78" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="79" spans="1:14">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17">
       <c r="A79" s="1">
         <f t="shared" si="8"/>
         <v>100610</v>
@@ -5245,16 +5352,16 @@
         <v>10</v>
       </c>
       <c r="D79" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E79" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F79" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G79" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H79">
         <v>0</v>
@@ -5275,10 +5382,10 @@
         <v>0</v>
       </c>
       <c r="N79" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="80" spans="1:16">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17">
       <c r="A80" s="1">
         <f t="shared" si="8"/>
         <v>100700</v>
@@ -5291,16 +5398,16 @@
         <v>0</v>
       </c>
       <c r="D80" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E80" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F80" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G80" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H80">
         <v>0</v>
@@ -5321,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="N80" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O80" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P80" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5343,16 +5450,16 @@
         <v>1</v>
       </c>
       <c r="D81" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E81" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F81" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G81" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H81">
         <v>3000</v>
@@ -5379,7 +5486,7 @@
         <v>40003</v>
       </c>
       <c r="P81" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5395,16 +5502,16 @@
         <v>2</v>
       </c>
       <c r="D82" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E82" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F82" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G82" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H82">
         <v>3500</v>
@@ -5431,7 +5538,7 @@
         <v>40003</v>
       </c>
       <c r="P82" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5447,16 +5554,16 @@
         <v>3</v>
       </c>
       <c r="D83" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E83" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F83" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G83" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H83">
         <v>4000</v>
@@ -5480,10 +5587,10 @@
         <v>60033</v>
       </c>
       <c r="O83" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P83" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5499,16 +5606,16 @@
         <v>4</v>
       </c>
       <c r="D84" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E84" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F84" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G84" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H84">
         <v>4500</v>
@@ -5532,10 +5639,10 @@
         <v>60034</v>
       </c>
       <c r="O84" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P84" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5551,16 +5658,16 @@
         <v>5</v>
       </c>
       <c r="D85" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E85" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F85" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G85" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H85">
         <v>5000</v>
@@ -5584,10 +5691,10 @@
         <v>60035</v>
       </c>
       <c r="O85" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P85" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5603,16 +5710,16 @@
         <v>6</v>
       </c>
       <c r="D86" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E86" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F86" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G86" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H86">
         <v>5500</v>
@@ -5636,10 +5743,10 @@
         <v>60036</v>
       </c>
       <c r="O86" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P86" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5655,16 +5762,16 @@
         <v>7</v>
       </c>
       <c r="D87" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E87" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F87" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G87" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H87">
         <v>6000</v>
@@ -5688,10 +5795,10 @@
         <v>60037</v>
       </c>
       <c r="O87" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P87" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5707,16 +5814,16 @@
         <v>8</v>
       </c>
       <c r="D88" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E88" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F88" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G88" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H88">
         <v>6500</v>
@@ -5740,10 +5847,10 @@
         <v>60038</v>
       </c>
       <c r="O88" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P88" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5759,16 +5866,16 @@
         <v>9</v>
       </c>
       <c r="D89" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E89" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F89" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G89" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H89">
         <v>7000</v>
@@ -5792,10 +5899,10 @@
         <v>60039</v>
       </c>
       <c r="O89" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P89" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5811,16 +5918,16 @@
         <v>10</v>
       </c>
       <c r="D90" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E90" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F90" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G90" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H90">
         <v>7500</v>
@@ -5841,13 +5948,13 @@
         <v>0</v>
       </c>
       <c r="N90" t="s">
+        <v>88</v>
+      </c>
+      <c r="O90" t="s">
         <v>87</v>
       </c>
-      <c r="O90" t="s">
-        <v>86</v>
-      </c>
       <c r="P90" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -5863,16 +5970,16 @@
         <v>0</v>
       </c>
       <c r="D91" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E91" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F91" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G91" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H91">
         <v>0</v>
@@ -5893,13 +6000,13 @@
         <v>0</v>
       </c>
       <c r="N91" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O91" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P91" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -5915,16 +6022,16 @@
         <v>1</v>
       </c>
       <c r="D92" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E92" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F92" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G92" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H92">
         <v>0</v>
@@ -5945,10 +6052,10 @@
         <v>0</v>
       </c>
       <c r="N92" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P92" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -5964,16 +6071,16 @@
         <v>2</v>
       </c>
       <c r="D93" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E93" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F93" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G93" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H93">
         <v>0</v>
@@ -5994,10 +6101,10 @@
         <v>0</v>
       </c>
       <c r="N93" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P93" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6013,16 +6120,16 @@
         <v>3</v>
       </c>
       <c r="D94" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E94" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F94" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G94" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H94">
         <v>0</v>
@@ -6043,10 +6150,10 @@
         <v>0</v>
       </c>
       <c r="N94" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P94" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6062,16 +6169,16 @@
         <v>4</v>
       </c>
       <c r="D95" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E95" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F95" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G95" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H95">
         <v>0</v>
@@ -6092,10 +6199,10 @@
         <v>0</v>
       </c>
       <c r="N95" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P95" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6111,16 +6218,16 @@
         <v>5</v>
       </c>
       <c r="D96" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E96" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F96" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G96" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H96">
         <v>0</v>
@@ -6141,10 +6248,10 @@
         <v>0</v>
       </c>
       <c r="N96" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P96" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6160,16 +6267,16 @@
         <v>6</v>
       </c>
       <c r="D97" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E97" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F97" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G97" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H97">
         <v>0</v>
@@ -6190,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="N97" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P97" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6209,16 +6316,16 @@
         <v>7</v>
       </c>
       <c r="D98" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E98" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F98" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G98" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H98">
         <v>0</v>
@@ -6239,10 +6346,10 @@
         <v>0</v>
       </c>
       <c r="N98" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P98" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6258,16 +6365,16 @@
         <v>8</v>
       </c>
       <c r="D99" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E99" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F99" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G99" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H99">
         <v>0</v>
@@ -6288,10 +6395,10 @@
         <v>0</v>
       </c>
       <c r="N99" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P99" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6307,16 +6414,16 @@
         <v>9</v>
       </c>
       <c r="D100" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E100" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F100" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G100" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H100">
         <v>0</v>
@@ -6337,10 +6444,10 @@
         <v>0</v>
       </c>
       <c r="N100" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P100" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6356,16 +6463,16 @@
         <v>10</v>
       </c>
       <c r="D101" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E101" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F101" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G101" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H101">
         <v>0</v>
@@ -6386,10 +6493,10 @@
         <v>0</v>
       </c>
       <c r="N101" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P101" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -6406,17 +6513,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/skill_config.xlsx
+++ b/Configs/skill_config.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="skill_config" sheetId="1" r:id="rId1"/>
-    <sheet name="skill_meta" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="102">
   <si>
     <t>id</t>
   </si>
@@ -334,12 +333,6 @@
   </si>
   <si>
     <t>60040|90010</t>
-  </si>
-  <si>
-    <t>slot_ids</t>
-  </si>
-  <si>
-    <t>1001|1002|1003|1004|1005|1006|1007|1008</t>
   </si>
 </sst>
 </file>
@@ -6503,31 +6496,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" t="s">
-        <v>103</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
 </file>